--- a/dashboard_output_SDG8.xlsx
+++ b/dashboard_output_SDG8.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q213"/>
+  <dimension ref="A1:P213"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -387,57 +387,52 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>reach_target_year</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>speed</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>pctl</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>end_year</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>end_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>start_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>indicator_sdg</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>indicatorname</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>start_year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>end_year</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>end_value</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>typical_end_value</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>indicator_sdg</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>indicatorname</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>start_value</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>reach_target_year</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>reach_target</t>
         </is>
       </c>
     </row>
@@ -466,16 +461,13 @@
           <t>ABW</t>
         </is>
       </c>
-      <c r="G2">
-        <v>0.92757451038163</v>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2">
+        <v>0.9232510533082389</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I2">
-        <v>2015</v>
       </c>
       <c r="J2">
         <v>2022</v>
@@ -484,7 +476,7 @@
         <v>29917.2</v>
       </c>
       <c r="L2">
-        <v>38563.46899342869</v>
+        <v>27458.4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -497,12 +489,10 @@
         </is>
       </c>
       <c r="O2">
-        <v>27458.4</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P2">
+        <v>30125.576770873</v>
       </c>
     </row>
     <row r="3">
@@ -530,16 +520,13 @@
           <t>AFG</t>
         </is>
       </c>
-      <c r="G3">
-        <v>-0.7552093289594467</v>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3">
+        <v>-0.7501487148862054</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I3">
-        <v>2015</v>
       </c>
       <c r="J3">
         <v>2020</v>
@@ -548,7 +535,7 @@
         <v>528</v>
       </c>
       <c r="L3">
-        <v>827.4661521254343</v>
+        <v>565.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -561,12 +548,10 @@
         </is>
       </c>
       <c r="O3">
-        <v>565.8</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P3">
+        <v>621.1881959058908</v>
       </c>
     </row>
     <row r="4">
@@ -594,16 +579,13 @@
           <t>AGO</t>
         </is>
       </c>
-      <c r="G4">
-        <v>-2.074033669152608</v>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4">
+        <v>-2.097276208450592</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I4">
-        <v>2015</v>
       </c>
       <c r="J4">
         <v>2022</v>
@@ -612,7 +594,7 @@
         <v>2382</v>
       </c>
       <c r="L4">
-        <v>5690.722646049158</v>
+        <v>3214.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -625,12 +607,10 @@
         </is>
       </c>
       <c r="O4">
-        <v>3214.2</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P4">
+        <v>3705.919589777768</v>
       </c>
     </row>
     <row r="5">
@@ -658,16 +638,13 @@
           <t>ALB</t>
         </is>
       </c>
-      <c r="G5">
-        <v>1.843701964844375</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5">
+        <v>1.865644356191163</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I5">
-        <v>2015</v>
       </c>
       <c r="J5">
         <v>2022</v>
@@ -676,7 +653,7 @@
         <v>5178.599999999999</v>
       </c>
       <c r="L5">
-        <v>7003.91144243892</v>
+        <v>3981.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -689,12 +666,10 @@
         </is>
       </c>
       <c r="O5">
-        <v>3981.6</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P5">
+        <v>4585.940794441016</v>
       </c>
     </row>
     <row r="6">
@@ -722,16 +697,13 @@
           <t>AND</t>
         </is>
       </c>
-      <c r="G6">
-        <v>0.3853704126382646</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6">
+        <v>0.3800847782524264</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I6">
-        <v>2015</v>
       </c>
       <c r="J6">
         <v>2022</v>
@@ -740,7 +712,7 @@
         <v>39780.6</v>
       </c>
       <c r="L6">
-        <v>50528.67816350098</v>
+        <v>38655</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -753,12 +725,10 @@
         </is>
       </c>
       <c r="O6">
-        <v>38655</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P6">
+        <v>41630.8795457068</v>
       </c>
     </row>
     <row r="7">
@@ -786,16 +756,13 @@
           <t>ARE</t>
         </is>
       </c>
-      <c r="G7">
-        <v>-0.2854851648362943</v>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7">
+        <v>-0.2811249416043487</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I7">
-        <v>2015</v>
       </c>
       <c r="J7">
         <v>2022</v>
@@ -804,7 +771,7 @@
         <v>42687.6</v>
       </c>
       <c r="L7">
-        <v>55447.49880546522</v>
+        <v>43534.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -817,12 +784,10 @@
         </is>
       </c>
       <c r="O7">
-        <v>43534.8</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P7">
+        <v>46562.40101513115</v>
       </c>
     </row>
     <row r="8">
@@ -850,16 +815,13 @@
           <t>ARG</t>
         </is>
       </c>
-      <c r="G8">
-        <v>-0.2961496503011501</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8">
+        <v>-0.2985882472418179</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I8">
-        <v>2015</v>
       </c>
       <c r="J8">
         <v>2022</v>
@@ -868,7 +830,7 @@
         <v>13182.6</v>
       </c>
       <c r="L8">
-        <v>21761.09772490714</v>
+        <v>13679.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -881,12 +843,10 @@
         </is>
       </c>
       <c r="O8">
-        <v>13679.4</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P8">
+        <v>15447.96285579383</v>
       </c>
     </row>
     <row r="9">
@@ -914,16 +874,13 @@
           <t>ARM</t>
         </is>
       </c>
-      <c r="G9">
-        <v>2.168015797389606</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9">
+        <v>2.193727547525226</v>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I9">
-        <v>2015</v>
       </c>
       <c r="J9">
         <v>2022</v>
@@ -932,7 +889,7 @@
         <v>4791</v>
       </c>
       <c r="L9">
-        <v>6203.847409786978</v>
+        <v>3512.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -945,12 +902,10 @@
         </is>
       </c>
       <c r="O9">
-        <v>3512.4</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P9">
+        <v>4048.247631186675</v>
       </c>
     </row>
     <row r="10">
@@ -978,16 +933,13 @@
           <t>ASM</t>
         </is>
       </c>
-      <c r="G10">
-        <v>0.5925779583992608</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10">
+        <v>0.5975364558562839</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I10">
-        <v>2015</v>
       </c>
       <c r="J10">
         <v>2022</v>
@@ -996,7 +948,7 @@
         <v>13708.8</v>
       </c>
       <c r="L10">
-        <v>20447.52451854495</v>
+        <v>12727.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1009,12 +961,10 @@
         </is>
       </c>
       <c r="O10">
-        <v>12727.2</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P10">
+        <v>14402.25200789792</v>
       </c>
     </row>
     <row r="11">
@@ -1042,16 +992,13 @@
           <t>ATG</t>
         </is>
       </c>
-      <c r="G11">
-        <v>0.6993121905634325</v>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11">
+        <v>0.7034942276239592</v>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I11">
-        <v>2015</v>
       </c>
       <c r="J11">
         <v>2022</v>
@@ -1060,7 +1007,7 @@
         <v>17457</v>
       </c>
       <c r="L11">
-        <v>24957.88178745187</v>
+        <v>16077.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1073,12 +1020,10 @@
         </is>
       </c>
       <c r="O11">
-        <v>16077.6</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P11">
+        <v>18062.14547065729</v>
       </c>
     </row>
     <row r="12">
@@ -1106,16 +1051,13 @@
           <t>AUS</t>
         </is>
       </c>
-      <c r="G12">
-        <v>1.477187867781148</v>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12">
+        <v>1.465159103331968</v>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I12">
-        <v>2015</v>
       </c>
       <c r="J12">
         <v>2022</v>
@@ -1124,7 +1066,7 @@
         <v>61009.8</v>
       </c>
       <c r="L12">
-        <v>67970.30632085486</v>
+        <v>56739</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1137,12 +1079,10 @@
         </is>
       </c>
       <c r="O12">
-        <v>56739</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P12">
+        <v>59669.03310814508</v>
       </c>
     </row>
     <row r="13">
@@ -1170,16 +1110,13 @@
           <t>AUT</t>
         </is>
       </c>
-      <c r="G13">
-        <v>1.118308330961668</v>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13">
+        <v>1.100923622839949</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I13">
-        <v>2015</v>
       </c>
       <c r="J13">
         <v>2022</v>
@@ -1188,7 +1125,7 @@
         <v>47251.2</v>
       </c>
       <c r="L13">
-        <v>55824.0571044168</v>
+        <v>43915.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1201,12 +1138,10 @@
         </is>
       </c>
       <c r="O13">
-        <v>43915.2</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P13">
+        <v>46944.8170446958</v>
       </c>
     </row>
     <row r="14">
@@ -1234,16 +1169,13 @@
           <t>AZE</t>
         </is>
       </c>
-      <c r="G14">
-        <v>0.1265609808269111</v>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14">
+        <v>0.1280581354568783</v>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I14">
-        <v>2015</v>
       </c>
       <c r="J14">
         <v>2022</v>
@@ -1252,7 +1184,7 @@
         <v>5599.8</v>
       </c>
       <c r="L14">
-        <v>9534.724468199078</v>
+        <v>5500.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1265,12 +1197,10 @@
         </is>
       </c>
       <c r="O14">
-        <v>5500.8</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P14">
+        <v>6319.064253314705</v>
       </c>
     </row>
     <row r="15">
@@ -1340,16 +1270,13 @@
           <t>BEL</t>
         </is>
       </c>
-      <c r="G16">
-        <v>1.249673162936412</v>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16">
+        <v>1.230758233099371</v>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I16">
-        <v>2015</v>
       </c>
       <c r="J16">
         <v>2022</v>
@@ -1358,7 +1285,7 @@
         <v>44596.8</v>
       </c>
       <c r="L16">
-        <v>52805.73109922658</v>
+        <v>40893.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1371,12 +1298,10 @@
         </is>
       </c>
       <c r="O16">
-        <v>40893.6</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P16">
+        <v>43899.18158647518</v>
       </c>
     </row>
     <row r="17">
@@ -1404,16 +1329,13 @@
           <t>BEN</t>
         </is>
       </c>
-      <c r="G17">
-        <v>1.390460497068424</v>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17">
+        <v>1.398194097623511</v>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I17">
-        <v>2015</v>
       </c>
       <c r="J17">
         <v>2022</v>
@@ -1422,7 +1344,7 @@
         <v>1218.6</v>
       </c>
       <c r="L17">
-        <v>1768.393038653954</v>
+        <v>1002.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1435,12 +1357,10 @@
         </is>
       </c>
       <c r="O17">
-        <v>1002.6</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P17">
+        <v>1152.450053524617</v>
       </c>
     </row>
     <row r="18">
@@ -1468,16 +1388,13 @@
           <t>BFA</t>
         </is>
       </c>
-      <c r="G18">
-        <v>1.200662059465722</v>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18">
+        <v>1.198762589724977</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I18">
-        <v>2015</v>
       </c>
       <c r="J18">
         <v>2022</v>
@@ -1486,7 +1403,7 @@
         <v>739.1999999999999</v>
       </c>
       <c r="L18">
-        <v>1086.609967309916</v>
+        <v>630</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1499,12 +1416,10 @@
         </is>
       </c>
       <c r="O18">
-        <v>630</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P18">
+        <v>719.7055175772377</v>
       </c>
     </row>
     <row r="19">
@@ -1532,16 +1447,13 @@
           <t>BGD</t>
         </is>
       </c>
-      <c r="G19">
-        <v>2.714166973772535</v>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19">
+        <v>2.736317673295356</v>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I19">
-        <v>2015</v>
       </c>
       <c r="J19">
         <v>2022</v>
@@ -1550,7 +1462,7 @@
         <v>1804.2</v>
       </c>
       <c r="L19">
-        <v>2171.664087779443</v>
+        <v>1224.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1563,12 +1475,10 @@
         </is>
       </c>
       <c r="O19">
-        <v>1224.6</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P19">
+        <v>1409.9346032091</v>
       </c>
     </row>
     <row r="20">
@@ -1596,16 +1506,13 @@
           <t>BGR</t>
         </is>
       </c>
-      <c r="G20">
-        <v>2.054425063784708</v>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20">
+        <v>2.076836410640961</v>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I20">
-        <v>2015</v>
       </c>
       <c r="J20">
         <v>2022</v>
@@ -1614,7 +1521,7 @@
         <v>9601.199999999999</v>
       </c>
       <c r="L20">
-        <v>12369.45998051732</v>
+        <v>7268.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1627,12 +1534,10 @@
         </is>
       </c>
       <c r="O20">
-        <v>7268.4</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P20">
+        <v>8320.603163655151</v>
       </c>
     </row>
     <row r="21">
@@ -1660,16 +1565,13 @@
           <t>BHR</t>
         </is>
       </c>
-      <c r="G21">
-        <v>0.6070338507262331</v>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21">
+        <v>0.6066804388517539</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I21">
-        <v>2015</v>
       </c>
       <c r="J21">
         <v>2022</v>
@@ -1678,7 +1580,7 @@
         <v>25234.2</v>
       </c>
       <c r="L21">
-        <v>34324.92750199398</v>
+        <v>23734.2</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1691,12 +1593,10 @@
         </is>
       </c>
       <c r="O21">
-        <v>23734.2</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P21">
+        <v>26231.23292936691</v>
       </c>
     </row>
     <row r="22">
@@ -1724,16 +1624,13 @@
           <t>BHS</t>
         </is>
       </c>
-      <c r="G22">
-        <v>0.5345020748889949</v>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22">
+        <v>0.5305549300384362</v>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I22">
-        <v>2015</v>
       </c>
       <c r="J22">
         <v>2022</v>
@@ -1742,7 +1639,7 @@
         <v>32186.4</v>
       </c>
       <c r="L22">
-        <v>42156.75861660541</v>
+        <v>30719.4</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1755,12 +1652,10 @@
         </is>
       </c>
       <c r="O22">
-        <v>30719.4</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P22">
+        <v>33505.39451051308</v>
       </c>
     </row>
     <row r="23">
@@ -1788,16 +1683,13 @@
           <t>BIH</t>
         </is>
       </c>
-      <c r="G23">
-        <v>2.16453113015515</v>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23">
+        <v>2.190132777998615</v>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I23">
-        <v>2015</v>
       </c>
       <c r="J23">
         <v>2022</v>
@@ -1806,7 +1698,7 @@
         <v>6327</v>
       </c>
       <c r="L23">
-        <v>8148.502658256789</v>
+        <v>4662</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1819,12 +1711,10 @@
         </is>
       </c>
       <c r="O23">
-        <v>4662</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P23">
+        <v>5363.628762080046</v>
       </c>
     </row>
     <row r="24">
@@ -1852,16 +1742,13 @@
           <t>BLR</t>
         </is>
       </c>
-      <c r="G24">
-        <v>0.2810280532153919</v>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24">
+        <v>0.2843207661586738</v>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I24">
-        <v>2015</v>
       </c>
       <c r="J24">
         <v>2022</v>
@@ -1870,7 +1757,7 @@
         <v>6206.4</v>
       </c>
       <c r="L24">
-        <v>10293.59081858016</v>
+        <v>5967</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1883,12 +1770,10 @@
         </is>
       </c>
       <c r="O24">
-        <v>5967</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P24">
+        <v>6848.520694250241</v>
       </c>
     </row>
     <row r="25">
@@ -1916,16 +1801,13 @@
           <t>BLZ</t>
         </is>
       </c>
-      <c r="G25">
-        <v>0.1327142364379565</v>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25">
+        <v>0.1342650743768193</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I25">
-        <v>2015</v>
       </c>
       <c r="J25">
         <v>2022</v>
@@ -1934,7 +1816,7 @@
         <v>6269.4</v>
       </c>
       <c r="L25">
-        <v>10596.02025099798</v>
+        <v>6154.2</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1947,12 +1829,10 @@
         </is>
       </c>
       <c r="O25">
-        <v>6154.2</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P25">
+        <v>7060.806868104962</v>
       </c>
     </row>
     <row r="26">
@@ -1980,6 +1860,9 @@
           <t>BMU</t>
         </is>
       </c>
+      <c r="G26">
+        <v>1997</v>
+      </c>
       <c r="J26">
         <v>2024</v>
       </c>
@@ -1996,14 +1879,6 @@
           <t>GDP per capita (constant 2015 US$)</t>
         </is>
       </c>
-      <c r="P26">
-        <v>1997</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>past</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2030,16 +1905,13 @@
           <t>BOL</t>
         </is>
       </c>
-      <c r="G27">
-        <v>0.3976806626884541</v>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27">
+        <v>0.4022490466012414</v>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I27">
-        <v>2015</v>
       </c>
       <c r="J27">
         <v>2022</v>
@@ -2048,7 +1920,7 @@
         <v>3172.8</v>
       </c>
       <c r="L27">
-        <v>5312.596288020803</v>
+        <v>2995.8</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2061,12 +1933,10 @@
         </is>
       </c>
       <c r="O27">
-        <v>2995.8</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P27">
+        <v>3454.905243772515</v>
       </c>
     </row>
     <row r="28">
@@ -2094,16 +1964,13 @@
           <t>BRA</t>
         </is>
       </c>
-      <c r="G28">
-        <v>0.07907667920294768</v>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28">
+        <v>0.07991944158318022</v>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I28">
-        <v>2015</v>
       </c>
       <c r="J28">
         <v>2022</v>
@@ -2112,7 +1979,7 @@
         <v>9031.799999999999</v>
       </c>
       <c r="L28">
-        <v>14942.06287345118</v>
+        <v>8936.4</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2125,12 +1992,10 @@
         </is>
       </c>
       <c r="O28">
-        <v>8936.4</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P28">
+        <v>10194.7658781985</v>
       </c>
     </row>
     <row r="29">
@@ -2158,16 +2023,13 @@
           <t>BRB</t>
         </is>
       </c>
-      <c r="G29">
-        <v>0.002522785535632011</v>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29">
+        <v>0.00253363980970432</v>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I29">
-        <v>2015</v>
       </c>
       <c r="J29">
         <v>2022</v>
@@ -2176,7 +2038,7 @@
         <v>18959.4</v>
       </c>
       <c r="L29">
-        <v>28606.42353651976</v>
+        <v>18954</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2189,12 +2051,10 @@
         </is>
       </c>
       <c r="O29">
-        <v>18954</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P29">
+        <v>21161.2430738714</v>
       </c>
     </row>
     <row r="30">
@@ -2222,16 +2082,13 @@
           <t>BRN</t>
         </is>
       </c>
-      <c r="G30">
-        <v>-0.7736631168218976</v>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30">
+        <v>-0.7693689079978542</v>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I30">
-        <v>2015</v>
       </c>
       <c r="J30">
         <v>2022</v>
@@ -2240,7 +2097,7 @@
         <v>28549.2</v>
       </c>
       <c r="L30">
-        <v>42054.32641918531</v>
+        <v>30625.2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2253,12 +2110,10 @@
         </is>
       </c>
       <c r="O30">
-        <v>30625.2</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P30">
+        <v>33408.10995300987</v>
       </c>
     </row>
     <row r="31">
@@ -2286,16 +2141,13 @@
           <t>BTN</t>
         </is>
       </c>
-      <c r="G31">
-        <v>0.8718949669023947</v>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31">
+        <v>0.8819459903867823</v>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I31">
-        <v>2015</v>
       </c>
       <c r="J31">
         <v>2022</v>
@@ -2304,7 +2156,7 @@
         <v>3349.8</v>
       </c>
       <c r="L31">
-        <v>5239.653365049079</v>
+        <v>2953.8</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2317,12 +2169,10 @@
         </is>
       </c>
       <c r="O31">
-        <v>2953.8</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P31">
+        <v>3406.604543359206</v>
       </c>
     </row>
     <row r="32">
@@ -2350,16 +2200,13 @@
           <t>BWA</t>
         </is>
       </c>
-      <c r="G32">
-        <v>1.104774023232299</v>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32">
+        <v>1.117546321100089</v>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I32">
-        <v>2015</v>
       </c>
       <c r="J32">
         <v>2022</v>
@@ -2368,7 +2215,7 @@
         <v>7159.8</v>
       </c>
       <c r="L32">
-        <v>10574.73778710728</v>
+        <v>6141</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2381,12 +2228,10 @@
         </is>
       </c>
       <c r="O32">
-        <v>6141</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P32">
+        <v>7045.843851747537</v>
       </c>
     </row>
     <row r="33">
@@ -2456,16 +2301,13 @@
           <t>CAN</t>
         </is>
       </c>
-      <c r="G34">
-        <v>0.6993965814367341</v>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34">
+        <v>0.6885479712258464</v>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I34">
-        <v>2015</v>
       </c>
       <c r="J34">
         <v>2022</v>
@@ -2474,7 +2316,7 @@
         <v>45677.4</v>
       </c>
       <c r="L34">
-        <v>55506.36341212989</v>
+        <v>43594.2</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2487,12 +2329,10 @@
         </is>
       </c>
       <c r="O34">
-        <v>43594.2</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P34">
+        <v>46622.13489546219</v>
       </c>
     </row>
     <row r="35">
@@ -2520,16 +2360,13 @@
           <t>CHE</t>
         </is>
       </c>
-      <c r="G35">
-        <v>0.6175853813116078</v>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35">
+        <v>0.6745266115867139</v>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I35">
-        <v>2015</v>
       </c>
       <c r="J35">
         <v>2020</v>
@@ -2538,7 +2375,7 @@
         <v>84637.2</v>
       </c>
       <c r="L35">
-        <v>88794.38195958352</v>
+        <v>83806.2</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2551,12 +2388,10 @@
         </is>
       </c>
       <c r="O35">
-        <v>83806.2</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P35">
+        <v>85027.87639249266</v>
       </c>
     </row>
     <row r="36">
@@ -2584,16 +2419,13 @@
           <t>CHI</t>
         </is>
       </c>
-      <c r="G36">
-        <v>2.054901109412169</v>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36">
+        <v>2.05678708072218</v>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I36">
-        <v>2015</v>
       </c>
       <c r="J36">
         <v>2022</v>
@@ -2602,7 +2434,7 @@
         <v>67513.8</v>
       </c>
       <c r="L36">
-        <v>72533.98950470657</v>
+        <v>61852.2</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2615,12 +2447,10 @@
         </is>
       </c>
       <c r="O36">
-        <v>61852.2</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P36">
+        <v>64653.40346655489</v>
       </c>
     </row>
     <row r="37">
@@ -2648,16 +2478,13 @@
           <t>CHL</t>
         </is>
       </c>
-      <c r="G37">
-        <v>0.4942062539596951</v>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37">
+        <v>0.4981430217760914</v>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I37">
-        <v>2015</v>
       </c>
       <c r="J37">
         <v>2022</v>
@@ -2666,7 +2493,7 @@
         <v>14283</v>
       </c>
       <c r="L37">
-        <v>21425.08275646931</v>
+        <v>13434</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2679,12 +2506,10 @@
         </is>
       </c>
       <c r="O37">
-        <v>13434</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P37">
+        <v>15178.88751476509</v>
       </c>
     </row>
     <row r="38">
@@ -2712,16 +2537,13 @@
           <t>CHN</t>
         </is>
       </c>
-      <c r="G38">
-        <v>2.792023081529627</v>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38">
+        <v>2.82048492975196</v>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I38">
-        <v>2015</v>
       </c>
       <c r="J38">
         <v>2022</v>
@@ -2730,7 +2552,7 @@
         <v>11830.8</v>
       </c>
       <c r="L38">
-        <v>13780.62380146534</v>
+        <v>8175.599999999999</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2743,12 +2565,10 @@
         </is>
       </c>
       <c r="O38">
-        <v>8175.599999999999</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P38">
+        <v>9341.680703773913</v>
       </c>
     </row>
     <row r="39">
@@ -2776,16 +2596,13 @@
           <t>CIV</t>
         </is>
       </c>
-      <c r="G39">
-        <v>1.419191580307309</v>
-      </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39">
+        <v>1.433420882732349</v>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I39">
-        <v>2015</v>
       </c>
       <c r="J39">
         <v>2022</v>
@@ -2794,7 +2611,7 @@
         <v>2227.2</v>
       </c>
       <c r="L39">
-        <v>3233.604134139314</v>
+        <v>1815</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2807,12 +2624,10 @@
         </is>
       </c>
       <c r="O39">
-        <v>1815</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P39">
+        <v>2093.431119897897</v>
       </c>
     </row>
     <row r="40">
@@ -2840,16 +2655,13 @@
           <t>CMR</t>
         </is>
       </c>
-      <c r="G40">
-        <v>0.2137654150415561</v>
-      </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40">
+        <v>0.2154681778711977</v>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I40">
-        <v>2015</v>
       </c>
       <c r="J40">
         <v>2022</v>
@@ -2858,7 +2670,7 @@
         <v>1458.6</v>
       </c>
       <c r="L40">
-        <v>2515.438668907557</v>
+        <v>1414.8</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2871,12 +2683,10 @@
         </is>
       </c>
       <c r="O40">
-        <v>1414.8</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P40">
+        <v>1630.327942114668</v>
       </c>
     </row>
     <row r="41">
@@ -2946,16 +2756,13 @@
           <t>COG</t>
         </is>
       </c>
-      <c r="G42">
-        <v>-2.562496677934852</v>
-      </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42">
+        <v>-2.588221578621504</v>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I42">
-        <v>2015</v>
       </c>
       <c r="J42">
         <v>2022</v>
@@ -2964,7 +2771,7 @@
         <v>1686</v>
       </c>
       <c r="L42">
-        <v>4340.661318370927</v>
+        <v>2439.6</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2977,12 +2784,10 @@
         </is>
       </c>
       <c r="O42">
-        <v>2439.6</v>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P42">
+        <v>2814.515513017637</v>
       </c>
     </row>
     <row r="43">
@@ -3010,16 +2815,13 @@
           <t>COL</t>
         </is>
       </c>
-      <c r="G43">
-        <v>0.6679225143579239</v>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43">
+        <v>0.6756638568436374</v>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I43">
-        <v>2015</v>
       </c>
       <c r="J43">
         <v>2022</v>
@@ -3028,7 +2830,7 @@
         <v>6856.8</v>
       </c>
       <c r="L43">
-        <v>10747.71213969256</v>
+        <v>6248.4</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3041,12 +2843,10 @@
         </is>
       </c>
       <c r="O43">
-        <v>6248.4</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P43">
+        <v>7167.562177809492</v>
       </c>
     </row>
     <row r="44">
@@ -3074,16 +2874,13 @@
           <t>COM</t>
         </is>
       </c>
-      <c r="G44">
-        <v>0.7928295231353673</v>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44">
+        <v>0.7990167644401254</v>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I44">
-        <v>2015</v>
       </c>
       <c r="J44">
         <v>2022</v>
@@ -3092,7 +2889,7 @@
         <v>1488.6</v>
       </c>
       <c r="L44">
-        <v>2361.64225849179</v>
+        <v>1329.6</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -3105,12 +2902,10 @@
         </is>
       </c>
       <c r="O44">
-        <v>1329.6</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P44">
+        <v>1531.626204178549</v>
       </c>
     </row>
     <row r="45">
@@ -3138,16 +2933,13 @@
           <t>CPV</t>
         </is>
       </c>
-      <c r="G45">
-        <v>1.09572033212692</v>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45">
+        <v>1.108630310293121</v>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I45">
-        <v>2015</v>
       </c>
       <c r="J45">
         <v>2022</v>
@@ -3156,7 +2948,7 @@
         <v>3997.8</v>
       </c>
       <c r="L45">
-        <v>6036.990507050201</v>
+        <v>3415.2</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -3169,12 +2961,10 @@
         </is>
       </c>
       <c r="O45">
-        <v>3415.2</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P45">
+        <v>3936.714872880895</v>
       </c>
     </row>
     <row r="46">
@@ -3202,16 +2992,13 @@
           <t>CRI</t>
         </is>
       </c>
-      <c r="G46">
-        <v>1.229102418034261</v>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46">
+        <v>1.239779985157643</v>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I46">
-        <v>2015</v>
       </c>
       <c r="J46">
         <v>2022</v>
@@ -3220,7 +3007,7 @@
         <v>13686</v>
       </c>
       <c r="L46">
-        <v>19021.62790560259</v>
+        <v>11715</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -3233,12 +3020,10 @@
         </is>
       </c>
       <c r="O46">
-        <v>11715</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P46">
+        <v>13285.76759816563</v>
       </c>
     </row>
     <row r="47">
@@ -3266,16 +3051,13 @@
           <t>CUB</t>
         </is>
       </c>
-      <c r="G47">
-        <v>-0.1679687063683072</v>
-      </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47">
+        <v>-0.1698538383954948</v>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I47">
-        <v>2015</v>
       </c>
       <c r="J47">
         <v>2022</v>
@@ -3284,7 +3066,7 @@
         <v>7552.2</v>
       </c>
       <c r="L47">
-        <v>13087.98907371925</v>
+        <v>7728</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -3297,12 +3079,10 @@
         </is>
       </c>
       <c r="O47">
-        <v>7728</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P47">
+        <v>8838.418369842309</v>
       </c>
     </row>
     <row r="48">
@@ -3330,16 +3110,13 @@
           <t>CUW</t>
         </is>
       </c>
-      <c r="G48">
-        <v>-0.9813284771176833</v>
-      </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48">
+        <v>-0.986037326309299</v>
+      </c>
+      <c r="I48" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I48">
-        <v>2015</v>
       </c>
       <c r="J48">
         <v>2022</v>
@@ -3348,7 +3125,7 @@
         <v>17307.6</v>
       </c>
       <c r="L48">
-        <v>29109.70073237913</v>
+        <v>19362</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -3361,12 +3138,10 @@
         </is>
       </c>
       <c r="O48">
-        <v>19362</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P48">
+        <v>21597.69324580314</v>
       </c>
     </row>
     <row r="49">
@@ -3394,16 +3169,13 @@
           <t>CYM</t>
         </is>
       </c>
-      <c r="G49">
-        <v>1.437318624145267</v>
-      </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49">
+        <v>1.50304618189708</v>
+      </c>
+      <c r="I49" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I49">
-        <v>2015</v>
       </c>
       <c r="J49">
         <v>2022</v>
@@ -3412,7 +3184,7 @@
         <v>79587.59999999999</v>
       </c>
       <c r="L49">
-        <v>84717.56331345443</v>
+        <v>76379.39999999999</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -3425,12 +3197,10 @@
         </is>
       </c>
       <c r="O49">
-        <v>76379.39999999999</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P49">
+        <v>78546.02053138588</v>
       </c>
     </row>
     <row r="50">
@@ -3458,16 +3228,13 @@
           <t>CYP</t>
         </is>
       </c>
-      <c r="G50">
-        <v>3.257760337784045</v>
-      </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50">
+        <v>3.245875568719839</v>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I50">
-        <v>2015</v>
       </c>
       <c r="J50">
         <v>2022</v>
@@ -3476,7 +3243,7 @@
         <v>31967.4</v>
       </c>
       <c r="L50">
-        <v>34037.66618285178</v>
+        <v>23487</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -3489,12 +3256,10 @@
         </is>
       </c>
       <c r="O50">
-        <v>23487</v>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P50">
+        <v>25971.1917492668</v>
       </c>
     </row>
     <row r="51">
@@ -3522,16 +3287,13 @@
           <t>CZE</t>
         </is>
       </c>
-      <c r="G51">
-        <v>1.247709716209507</v>
-      </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51">
+        <v>1.252759147797121</v>
+      </c>
+      <c r="I51" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I51">
-        <v>2015</v>
       </c>
       <c r="J51">
         <v>2022</v>
@@ -3540,7 +3302,7 @@
         <v>20627.4</v>
       </c>
       <c r="L51">
-        <v>27330.50623613829</v>
+        <v>17931.6</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -3553,12 +3315,10 @@
         </is>
       </c>
       <c r="O51">
-        <v>17931.6</v>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P51">
+        <v>20064.17379337416</v>
       </c>
     </row>
     <row r="52">
@@ -3586,16 +3346,13 @@
           <t>DEU</t>
         </is>
       </c>
-      <c r="G52">
-        <v>0.7648943315382033</v>
-      </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52">
+        <v>0.7532359664723458</v>
+      </c>
+      <c r="I52" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I52">
-        <v>2015</v>
       </c>
       <c r="J52">
         <v>2022</v>
@@ -3604,7 +3361,7 @@
         <v>44180.4</v>
       </c>
       <c r="L52">
-        <v>53829.22827054201</v>
+        <v>41911.2</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -3617,12 +3374,10 @@
         </is>
       </c>
       <c r="O52">
-        <v>41911.2</v>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P52">
+        <v>44926.92923704173</v>
       </c>
     </row>
     <row r="53">
@@ -3650,16 +3405,13 @@
           <t>DJI</t>
         </is>
       </c>
-      <c r="G53">
-        <v>1.520225319968367</v>
-      </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53">
+        <v>1.53709252287825</v>
+      </c>
+      <c r="I53" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I53">
-        <v>2015</v>
       </c>
       <c r="J53">
         <v>2022</v>
@@ -3668,7 +3420,7 @@
         <v>2959.8</v>
       </c>
       <c r="L53">
-        <v>4228.695062063673</v>
+        <v>2376</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -3681,12 +3433,10 @@
         </is>
       </c>
       <c r="O53">
-        <v>2376</v>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P53">
+        <v>2741.184868860526</v>
       </c>
     </row>
     <row r="54">
@@ -3714,16 +3464,13 @@
           <t>DMA</t>
         </is>
       </c>
-      <c r="G54">
-        <v>0.2700036697584177</v>
-      </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54">
+        <v>0.272947128329605</v>
+      </c>
+      <c r="I54" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I54">
-        <v>2015</v>
       </c>
       <c r="J54">
         <v>2022</v>
@@ -3732,7 +3479,7 @@
         <v>8590.799999999999</v>
       </c>
       <c r="L54">
-        <v>13944.8621105226</v>
+        <v>8282.4</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -3745,12 +3492,10 @@
         </is>
       </c>
       <c r="O54">
-        <v>8282.4</v>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P54">
+        <v>9461.612022996324</v>
       </c>
     </row>
     <row r="55">
@@ -3778,16 +3523,13 @@
           <t>DNK</t>
         </is>
       </c>
-      <c r="G55">
-        <v>2.446250776283267</v>
-      </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55">
+        <v>2.420927146799946</v>
+      </c>
+      <c r="I55" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I55">
-        <v>2015</v>
       </c>
       <c r="J55">
         <v>2022</v>
@@ -3796,7 +3538,7 @@
         <v>60248.39999999999</v>
       </c>
       <c r="L55">
-        <v>64622.75168457182</v>
+        <v>53094</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -3809,12 +3551,10 @@
         </is>
       </c>
       <c r="O55">
-        <v>53094</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P55">
+        <v>56085.13062119842</v>
       </c>
     </row>
     <row r="56">
@@ -3842,16 +3582,13 @@
           <t>DOM</t>
         </is>
       </c>
-      <c r="G56">
-        <v>1.798083519630901</v>
-      </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56">
+        <v>1.818190766986561</v>
+      </c>
+      <c r="I56" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I56">
-        <v>2015</v>
       </c>
       <c r="J56">
         <v>2022</v>
@@ -3860,7 +3597,7 @@
         <v>8698.199999999999</v>
       </c>
       <c r="L56">
-        <v>11631.00513061318</v>
+        <v>6801</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -3873,12 +3610,10 @@
         </is>
       </c>
       <c r="O56">
-        <v>6801</v>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P56">
+        <v>7792.89901867316</v>
       </c>
     </row>
     <row r="57">
@@ -3906,16 +3641,13 @@
           <t>DZA</t>
         </is>
       </c>
-      <c r="G57">
-        <v>-0.2135352066207556</v>
-      </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57">
+        <v>-0.2160799897754251</v>
+      </c>
+      <c r="I57" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I57">
-        <v>2015</v>
       </c>
       <c r="J57">
         <v>2022</v>
@@ -3924,7 +3656,7 @@
         <v>4544.4</v>
       </c>
       <c r="L57">
-        <v>8186.541814278205</v>
+        <v>4684.8</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -3937,12 +3669,10 @@
         </is>
       </c>
       <c r="O57">
-        <v>4684.8</v>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P57">
+        <v>5389.647196727023</v>
       </c>
     </row>
     <row r="58">
@@ -3970,16 +3700,13 @@
           <t>ECU</t>
         </is>
       </c>
-      <c r="G58">
-        <v>0.1552926833605812</v>
-      </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58">
+        <v>0.1571138074582288</v>
+      </c>
+      <c r="I58" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I58">
-        <v>2015</v>
       </c>
       <c r="J58">
         <v>2022</v>
@@ -3988,7 +3715,7 @@
         <v>6107.4</v>
       </c>
       <c r="L58">
-        <v>10308.1606142594</v>
+        <v>5976</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -4001,12 +3728,10 @@
         </is>
       </c>
       <c r="O58">
-        <v>5976</v>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P58">
+        <v>6858.73088665221</v>
       </c>
     </row>
     <row r="59">
@@ -4034,16 +3759,13 @@
           <t>EGY</t>
         </is>
       </c>
-      <c r="G59">
-        <v>1.373960052689284</v>
-      </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59">
+        <v>1.390124233848452</v>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I59">
-        <v>2015</v>
       </c>
       <c r="J59">
         <v>2022</v>
@@ -4052,7 +3774,7 @@
         <v>4029.6</v>
       </c>
       <c r="L59">
-        <v>5851.141644411255</v>
+        <v>3307.2</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -4065,12 +3787,10 @@
         </is>
       </c>
       <c r="O59">
-        <v>3307.2</v>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P59">
+        <v>3812.731685560839</v>
       </c>
     </row>
     <row r="60">
@@ -4140,16 +3860,13 @@
           <t>ESP</t>
         </is>
       </c>
-      <c r="G61">
-        <v>0.8387108785491445</v>
-      </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61">
+        <v>0.8361357431643667</v>
+      </c>
+      <c r="I61" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I61">
-        <v>2015</v>
       </c>
       <c r="J61">
         <v>2022</v>
@@ -4158,7 +3875,7 @@
         <v>28152.6</v>
       </c>
       <c r="L61">
-        <v>36902.49111568238</v>
+        <v>25982.4</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -4171,12 +3888,10 @@
         </is>
       </c>
       <c r="O61">
-        <v>25982.4</v>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P61">
+        <v>28587.05572131578</v>
       </c>
     </row>
     <row r="62">
@@ -4204,16 +3919,13 @@
           <t>EST</t>
         </is>
       </c>
-      <c r="G62">
-        <v>1.549246272367148</v>
-      </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62">
+        <v>1.555366980415824</v>
+      </c>
+      <c r="I62" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I62">
-        <v>2015</v>
       </c>
       <c r="J62">
         <v>2022</v>
@@ -4222,7 +3934,7 @@
         <v>21080.4</v>
       </c>
       <c r="L62">
-        <v>27066.45599075411</v>
+        <v>17722.2</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -4235,12 +3947,10 @@
         </is>
       </c>
       <c r="O62">
-        <v>17722.2</v>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P62">
+        <v>19838.87447526375</v>
       </c>
     </row>
     <row r="63">
@@ -4268,16 +3978,13 @@
           <t>ETH</t>
         </is>
       </c>
-      <c r="G63">
-        <v>2.275728535059179</v>
-      </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63">
+        <v>2.274527935008393</v>
+      </c>
+      <c r="I63" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I63">
-        <v>2015</v>
       </c>
       <c r="J63">
         <v>2022</v>
@@ -4286,7 +3993,7 @@
         <v>843.6</v>
       </c>
       <c r="L63">
-        <v>1071.167411507691</v>
+        <v>621.6</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -4299,12 +4006,10 @@
         </is>
       </c>
       <c r="O63">
-        <v>621.6</v>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P63">
+        <v>709.9410824796377</v>
       </c>
     </row>
     <row r="64">
@@ -4332,16 +4037,13 @@
           <t>FIN</t>
         </is>
       </c>
-      <c r="G64">
-        <v>1.161367403736473</v>
-      </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64">
+        <v>1.143430672062883</v>
+      </c>
+      <c r="I64" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I64">
-        <v>2015</v>
       </c>
       <c r="J64">
         <v>2022</v>
@@ -4350,7 +4052,7 @@
         <v>46016.4</v>
       </c>
       <c r="L64">
-        <v>54478.45899557239</v>
+        <v>42560.4</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -4363,12 +4065,10 @@
         </is>
       </c>
       <c r="O64">
-        <v>42560.4</v>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P64">
+        <v>45581.51222645266</v>
       </c>
     </row>
     <row r="65">
@@ -4396,16 +4096,13 @@
           <t>FJI</t>
         </is>
       </c>
-      <c r="G65">
-        <v>0.3584371390985796</v>
-      </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65">
+        <v>0.362694542458168</v>
+      </c>
+      <c r="I65" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I65">
-        <v>2015</v>
       </c>
       <c r="J65">
         <v>2022</v>
@@ -4414,7 +4111,7 @@
         <v>5362.8</v>
       </c>
       <c r="L65">
-        <v>8871.765461551209</v>
+        <v>5097.599999999999</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -4427,12 +4124,10 @@
         </is>
       </c>
       <c r="O65">
-        <v>5097.599999999999</v>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P65">
+        <v>5860.253055784896</v>
       </c>
     </row>
     <row r="66">
@@ -4460,16 +4155,13 @@
           <t>FRA</t>
         </is>
       </c>
-      <c r="G66">
-        <v>0.7520541841918771</v>
-      </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66">
+        <v>0.7424229703177048</v>
+      </c>
+      <c r="I66" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I66">
-        <v>2015</v>
       </c>
       <c r="J66">
         <v>2022</v>
@@ -4478,7 +4170,7 @@
         <v>38881.2</v>
       </c>
       <c r="L66">
-        <v>48513.53332251664</v>
+        <v>36702.6</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -4491,12 +4183,10 @@
         </is>
       </c>
       <c r="O66">
-        <v>36702.6</v>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P66">
+        <v>39644.21538744865</v>
       </c>
     </row>
     <row r="67">
@@ -4524,16 +4214,13 @@
           <t>FRO</t>
         </is>
       </c>
-      <c r="G67">
-        <v>1.763396132495854</v>
-      </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67">
+        <v>1.742692015323696</v>
+      </c>
+      <c r="I67" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I67">
-        <v>2015</v>
       </c>
       <c r="J67">
         <v>2022</v>
@@ -4542,7 +4229,7 @@
         <v>57829.2</v>
       </c>
       <c r="L67">
-        <v>64195.47445351239</v>
+        <v>52635</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -4555,12 +4242,10 @@
         </is>
       </c>
       <c r="O67">
-        <v>52635</v>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P67">
+        <v>55631.99395654888</v>
       </c>
     </row>
     <row r="68">
@@ -4588,16 +4273,13 @@
           <t>FSM</t>
         </is>
       </c>
-      <c r="G68">
-        <v>0.0440907708663149</v>
-      </c>
-      <c r="H68" t="inlineStr">
+      <c r="H68">
+        <v>0.04459176873399023</v>
+      </c>
+      <c r="I68" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I68">
-        <v>2015</v>
       </c>
       <c r="J68">
         <v>2022</v>
@@ -4606,7 +4288,7 @@
         <v>2929.8</v>
       </c>
       <c r="L68">
-        <v>5165.594101783719</v>
+        <v>2911.2</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -4619,12 +4301,10 @@
         </is>
       </c>
       <c r="O68">
-        <v>2911.2</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P68">
+        <v>3357.604499336488</v>
       </c>
     </row>
     <row r="69">
@@ -4652,16 +4332,13 @@
           <t>GAB</t>
         </is>
       </c>
-      <c r="G69">
-        <v>-0.5523700645785985</v>
-      </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69">
+        <v>-0.5587327549561881</v>
+      </c>
+      <c r="I69" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I69">
-        <v>2015</v>
       </c>
       <c r="J69">
         <v>2022</v>
@@ -4670,7 +4347,7 @@
         <v>6527.4</v>
       </c>
       <c r="L69">
-        <v>12020.64497719842</v>
+        <v>7047</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -4683,12 +4360,10 @@
         </is>
       </c>
       <c r="O69">
-        <v>7047</v>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P69">
+        <v>8070.776988801482</v>
       </c>
     </row>
     <row r="70">
@@ -4716,16 +4391,13 @@
           <t>GBR</t>
         </is>
       </c>
-      <c r="G70">
-        <v>0.903750436151922</v>
-      </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70">
+        <v>0.8896956660995069</v>
+      </c>
+      <c r="I70" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I70">
-        <v>2015</v>
       </c>
       <c r="J70">
         <v>2022</v>
@@ -4734,7 +4406,7 @@
         <v>47682.6</v>
       </c>
       <c r="L70">
-        <v>56876.65345255417</v>
+        <v>44983.8</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -4747,12 +4419,10 @@
         </is>
       </c>
       <c r="O70">
-        <v>44983.8</v>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P70">
+        <v>48017.53100149397</v>
       </c>
     </row>
     <row r="71">
@@ -4780,16 +4450,13 @@
           <t>GEO</t>
         </is>
       </c>
-      <c r="G71">
-        <v>2.387316143868365</v>
-      </c>
-      <c r="H71" t="inlineStr">
+      <c r="H71">
+        <v>2.415692695347409</v>
+      </c>
+      <c r="I71" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I71">
-        <v>2015</v>
       </c>
       <c r="J71">
         <v>2022</v>
@@ -4798,7 +4465,7 @@
         <v>5736.599999999999</v>
       </c>
       <c r="L71">
-        <v>7181.742861273463</v>
+        <v>4086.6</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -4811,12 +4478,10 @@
         </is>
       </c>
       <c r="O71">
-        <v>4086.6</v>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P71">
+        <v>4706.111149132642</v>
       </c>
     </row>
     <row r="72">
@@ -4844,16 +4509,13 @@
           <t>GHA</t>
         </is>
       </c>
-      <c r="G72">
-        <v>1.265578324517293</v>
-      </c>
-      <c r="H72" t="inlineStr">
+      <c r="H72">
+        <v>1.277862898931967</v>
+      </c>
+      <c r="I72" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I72">
-        <v>2015</v>
       </c>
       <c r="J72">
         <v>2022</v>
@@ -4862,7 +4524,7 @@
         <v>2067</v>
       </c>
       <c r="L72">
-        <v>3068.409239269652</v>
+        <v>1722.6</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -4875,12 +4537,10 @@
         </is>
       </c>
       <c r="O72">
-        <v>1722.6</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P72">
+        <v>1986.583896841158</v>
       </c>
     </row>
     <row r="73">
@@ -4908,16 +4568,13 @@
           <t>GIN</t>
         </is>
       </c>
-      <c r="G73">
-        <v>2.031180079441762</v>
-      </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73">
+        <v>2.035910962328716</v>
+      </c>
+      <c r="I73" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I73">
-        <v>2015</v>
       </c>
       <c r="J73">
         <v>2022</v>
@@ -4926,7 +4583,7 @@
         <v>987.5999999999999</v>
       </c>
       <c r="L73">
-        <v>1302.467053907523</v>
+        <v>747.6</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -4939,12 +4596,10 @@
         </is>
       </c>
       <c r="O73">
-        <v>747.6</v>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P73">
+        <v>856.3682524488623</v>
       </c>
     </row>
     <row r="74">
@@ -4972,16 +4627,13 @@
           <t>GMB</t>
         </is>
       </c>
-      <c r="G74">
-        <v>1.02904964327586</v>
-      </c>
-      <c r="H74" t="inlineStr">
+      <c r="H74">
+        <v>1.026848816092078</v>
+      </c>
+      <c r="I74" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I74">
-        <v>2015</v>
       </c>
       <c r="J74">
         <v>2022</v>
@@ -4990,7 +4642,7 @@
         <v>710.4</v>
       </c>
       <c r="L74">
-        <v>1067.858296575717</v>
+        <v>619.8</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -5003,12 +4655,10 @@
         </is>
       </c>
       <c r="O74">
-        <v>619.8</v>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P74">
+        <v>707.8485316511805</v>
       </c>
     </row>
     <row r="75">
@@ -5036,16 +4686,13 @@
           <t>GNB</t>
         </is>
       </c>
-      <c r="G75">
-        <v>1.135615041374434</v>
-      </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75">
+        <v>1.134252379042225</v>
+      </c>
+      <c r="I75" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I75">
-        <v>2015</v>
       </c>
       <c r="J75">
         <v>2022</v>
@@ -5054,7 +4701,7 @@
         <v>750.6</v>
       </c>
       <c r="L75">
-        <v>1114.177402842568</v>
+        <v>645</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -5067,12 +4714,10 @@
         </is>
       </c>
       <c r="O75">
-        <v>645</v>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P75">
+        <v>737.1409204752998</v>
       </c>
     </row>
     <row r="76">
@@ -5100,16 +4745,13 @@
           <t>GNQ</t>
         </is>
       </c>
-      <c r="G76">
-        <v>-3.595157626500375</v>
-      </c>
-      <c r="H76" t="inlineStr">
+      <c r="H76">
+        <v>-3.635976699238045</v>
+      </c>
+      <c r="I76" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I76">
-        <v>2015</v>
       </c>
       <c r="J76">
         <v>2022</v>
@@ -5118,7 +4760,7 @@
         <v>5524.2</v>
       </c>
       <c r="L76">
-        <v>15142.47845303908</v>
+        <v>9069</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -5131,12 +4773,10 @@
         </is>
       </c>
       <c r="O76">
-        <v>9069</v>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P76">
+        <v>10343.1519019682</v>
       </c>
     </row>
     <row r="77">
@@ -5164,16 +4804,13 @@
           <t>GRC</t>
         </is>
       </c>
-      <c r="G77">
-        <v>1.209787899884028</v>
-      </c>
-      <c r="H77" t="inlineStr">
+      <c r="H77">
+        <v>1.214674871349449</v>
+      </c>
+      <c r="I77" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I77">
-        <v>2015</v>
       </c>
       <c r="J77">
         <v>2022</v>
@@ -5182,7 +4819,7 @@
         <v>20595.6</v>
       </c>
       <c r="L77">
-        <v>27392.40861000827</v>
+        <v>17980.8</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -5195,12 +4832,10 @@
         </is>
       </c>
       <c r="O77">
-        <v>17980.8</v>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P77">
+        <v>20117.07923144906</v>
       </c>
     </row>
     <row r="78">
@@ -5228,16 +4863,13 @@
           <t>GRD</t>
         </is>
       </c>
-      <c r="G78">
-        <v>0.5868889702184187</v>
-      </c>
-      <c r="H78" t="inlineStr">
+      <c r="H78">
+        <v>0.5931293855420888</v>
+      </c>
+      <c r="I78" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I78">
-        <v>2015</v>
       </c>
       <c r="J78">
         <v>2022</v>
@@ -5246,7 +4878,7 @@
         <v>9406.199999999999</v>
       </c>
       <c r="L78">
-        <v>14574.16014423559</v>
+        <v>8694</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -5259,12 +4891,10 @@
         </is>
       </c>
       <c r="O78">
-        <v>8694</v>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P78">
+        <v>9923.278627688471</v>
       </c>
     </row>
     <row r="79">
@@ -5292,16 +4922,13 @@
           <t>GRL</t>
         </is>
       </c>
-      <c r="G79">
-        <v>1.721968009900479</v>
-      </c>
-      <c r="H79" t="inlineStr">
+      <c r="H79">
+        <v>1.695400307439862</v>
+      </c>
+      <c r="I79" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I79">
-        <v>2015</v>
       </c>
       <c r="J79">
         <v>2022</v>
@@ -5310,7 +4937,7 @@
         <v>49679.4</v>
       </c>
       <c r="L79">
-        <v>56436.68922771528</v>
+        <v>44536.2</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -5323,12 +4950,10 @@
         </is>
       </c>
       <c r="O79">
-        <v>44536.2</v>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P79">
+        <v>47568.48544964584</v>
       </c>
     </row>
     <row r="80">
@@ -5356,16 +4981,13 @@
           <t>GTM</t>
         </is>
       </c>
-      <c r="G80">
-        <v>0.8310236079769433</v>
-      </c>
-      <c r="H80" t="inlineStr">
+      <c r="H80">
+        <v>0.8408966812132276</v>
+      </c>
+      <c r="I80" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I80">
-        <v>2015</v>
       </c>
       <c r="J80">
         <v>2022</v>
@@ -5374,7 +4996,7 @@
         <v>4385.4</v>
       </c>
       <c r="L80">
-        <v>6854.192266461278</v>
+        <v>3893.4</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -5387,12 +5009,10 @@
         </is>
       </c>
       <c r="O80">
-        <v>3893.4</v>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P80">
+        <v>4484.953233858219</v>
       </c>
     </row>
     <row r="81">
@@ -5420,16 +5040,13 @@
           <t>GUM</t>
         </is>
       </c>
-      <c r="G81">
-        <v>-0.1896661186811213</v>
-      </c>
-      <c r="H81" t="inlineStr">
+      <c r="H81">
+        <v>-0.1876612957432988</v>
+      </c>
+      <c r="I81" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I81">
-        <v>2015</v>
       </c>
       <c r="J81">
         <v>2022</v>
@@ -5438,7 +5055,7 @@
         <v>34627.8</v>
       </c>
       <c r="L81">
-        <v>46907.80712392017</v>
+        <v>35166</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -5451,12 +5068,10 @@
         </is>
       </c>
       <c r="O81">
-        <v>35166</v>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P81">
+        <v>38075.05607641831</v>
       </c>
     </row>
     <row r="82">
@@ -5484,16 +5099,13 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G82">
-        <v>8.599589354044358</v>
-      </c>
-      <c r="H82" t="inlineStr">
+      <c r="H82">
+        <v>8.682369058175365</v>
+      </c>
+      <c r="I82" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I82">
-        <v>2015</v>
       </c>
       <c r="J82">
         <v>2022</v>
@@ -5502,7 +5114,7 @@
         <v>17365.2</v>
       </c>
       <c r="L82">
-        <v>9763.145959411535</v>
+        <v>5640.599999999999</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -5515,12 +5127,10 @@
         </is>
       </c>
       <c r="O82">
-        <v>5640.599999999999</v>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P82">
+        <v>6477.950411699565</v>
       </c>
     </row>
     <row r="83">
@@ -5548,16 +5158,13 @@
           <t>HKG</t>
         </is>
       </c>
-      <c r="G83">
-        <v>0.2865123829259346</v>
-      </c>
-      <c r="H83" t="inlineStr">
+      <c r="H83">
+        <v>0.2821539799387227</v>
+      </c>
+      <c r="I83" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I83">
-        <v>2015</v>
       </c>
       <c r="J83">
         <v>2022</v>
@@ -5566,7 +5173,7 @@
         <v>43281.6</v>
       </c>
       <c r="L83">
-        <v>54350.28228145297</v>
+        <v>42432</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -5579,12 +5186,10 @@
         </is>
       </c>
       <c r="O83">
-        <v>42432</v>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P83">
+        <v>45452.11490757555</v>
       </c>
     </row>
     <row r="84">
@@ -5612,16 +5217,13 @@
           <t>HND</t>
         </is>
       </c>
-      <c r="G84">
-        <v>0.6153156329406296</v>
-      </c>
-      <c r="H84" t="inlineStr">
+      <c r="H84">
+        <v>0.6219247600352114</v>
+      </c>
+      <c r="I84" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I84">
-        <v>2015</v>
       </c>
       <c r="J84">
         <v>2022</v>
@@ -5630,7 +5232,7 @@
         <v>2482.2</v>
       </c>
       <c r="L84">
-        <v>4043.470613177177</v>
+        <v>2271</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -5643,12 +5245,10 @@
         </is>
       </c>
       <c r="O84">
-        <v>2271</v>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P84">
+        <v>2620.073631262369</v>
       </c>
     </row>
     <row r="85">
@@ -5676,16 +5276,13 @@
           <t>HRV</t>
         </is>
       </c>
-      <c r="G85">
-        <v>2.457313052222958</v>
-      </c>
-      <c r="H85" t="inlineStr">
+      <c r="H85">
+        <v>2.476013309274411</v>
+      </c>
+      <c r="I85" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I85">
-        <v>2015</v>
       </c>
       <c r="J85">
         <v>2022</v>
@@ -5694,7 +5291,7 @@
         <v>16616.4</v>
       </c>
       <c r="L85">
-        <v>19829.24962189882</v>
+        <v>12285.6</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -5707,12 +5304,10 @@
         </is>
       </c>
       <c r="O85">
-        <v>12285.6</v>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P85">
+        <v>13915.77562245406</v>
       </c>
     </row>
     <row r="86">
@@ -5740,16 +5335,13 @@
           <t>HTI</t>
         </is>
       </c>
-      <c r="G86">
-        <v>-0.8145279619189937</v>
-      </c>
-      <c r="H86" t="inlineStr">
+      <c r="H86">
+        <v>-0.8205179562809397</v>
+      </c>
+      <c r="I86" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I86">
-        <v>2015</v>
       </c>
       <c r="J86">
         <v>2022</v>
@@ -5758,7 +5350,7 @@
         <v>1257</v>
       </c>
       <c r="L86">
-        <v>2508.946897254641</v>
+        <v>1411.2</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -5771,12 +5363,10 @@
         </is>
       </c>
       <c r="O86">
-        <v>1411.2</v>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P86">
+        <v>1626.158017269359</v>
       </c>
     </row>
     <row r="87">
@@ -5804,16 +5394,13 @@
           <t>HUN</t>
         </is>
       </c>
-      <c r="G87">
-        <v>2.08828183789605</v>
-      </c>
-      <c r="H87" t="inlineStr">
+      <c r="H87">
+        <v>2.103890833041857</v>
+      </c>
+      <c r="I87" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I87">
-        <v>2015</v>
       </c>
       <c r="J87">
         <v>2022</v>
@@ -5822,7 +5409,7 @@
         <v>16506.6</v>
       </c>
       <c r="L87">
-        <v>20525.23440043096</v>
+        <v>12783</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -5835,12 +5422,10 @@
         </is>
       </c>
       <c r="O87">
-        <v>12783</v>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P87">
+        <v>14463.65431987504</v>
       </c>
     </row>
     <row r="88">
@@ -5868,16 +5453,13 @@
           <t>IDN</t>
         </is>
       </c>
-      <c r="G88">
-        <v>1.40602971119493</v>
-      </c>
-      <c r="H88" t="inlineStr">
+      <c r="H88">
+        <v>1.422564934193531</v>
+      </c>
+      <c r="I88" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I88">
-        <v>2015</v>
       </c>
       <c r="J88">
         <v>2022</v>
@@ -5886,7 +5468,7 @@
         <v>4024.8</v>
       </c>
       <c r="L88">
-        <v>5818.052095917415</v>
+        <v>3288</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -5899,12 +5481,10 @@
         </is>
       </c>
       <c r="O88">
-        <v>3288</v>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P88">
+        <v>3790.683770071153</v>
       </c>
     </row>
     <row r="89">
@@ -5932,16 +5512,13 @@
           <t>IMN</t>
         </is>
       </c>
-      <c r="G89">
-        <v>0.7466224378824791</v>
-      </c>
-      <c r="H89" t="inlineStr">
+      <c r="H89">
+        <v>0.8253168811100815</v>
+      </c>
+      <c r="I89" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I89">
-        <v>2015</v>
       </c>
       <c r="J89">
         <v>2022</v>
@@ -5950,7 +5527,7 @@
         <v>86103.59999999999</v>
       </c>
       <c r="L89">
-        <v>89884.2</v>
+        <v>84753.59999999999</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -5963,12 +5540,10 @@
         </is>
       </c>
       <c r="O89">
-        <v>84753.59999999999</v>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P89">
+        <v>86378.74247343582</v>
       </c>
     </row>
     <row r="90">
@@ -5996,16 +5571,13 @@
           <t>IND</t>
         </is>
       </c>
-      <c r="G90">
-        <v>1.954090317649551</v>
-      </c>
-      <c r="H90" t="inlineStr">
+      <c r="H90">
+        <v>1.972666125681095</v>
+      </c>
+      <c r="I90" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I90">
-        <v>2015</v>
       </c>
       <c r="J90">
         <v>2022</v>
@@ -6014,7 +5586,7 @@
         <v>2098.2</v>
       </c>
       <c r="L90">
-        <v>2819.922477691052</v>
+        <v>1584</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -6027,12 +5599,10 @@
         </is>
       </c>
       <c r="O90">
-        <v>1584</v>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P90">
+        <v>1826.227028855482</v>
       </c>
     </row>
     <row r="91">
@@ -6060,16 +5630,13 @@
           <t>IRL</t>
         </is>
       </c>
-      <c r="G91">
-        <v>9.500679289922118</v>
-      </c>
-      <c r="H91" t="inlineStr">
+      <c r="H91">
+        <v>9.752077070917665</v>
+      </c>
+      <c r="I91" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I91">
-        <v>2015</v>
       </c>
       <c r="J91">
         <v>2020</v>
@@ -6078,7 +5645,7 @@
         <v>80908.8</v>
       </c>
       <c r="L91">
-        <v>71872.72344330633</v>
+        <v>64311.6</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -6091,12 +5658,10 @@
         </is>
       </c>
       <c r="O91">
-        <v>64311.6</v>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P91">
+        <v>66265.42744756975</v>
       </c>
     </row>
     <row r="92">
@@ -6124,16 +5689,13 @@
           <t>IRN</t>
         </is>
       </c>
-      <c r="G92">
-        <v>0.689331815285036</v>
-      </c>
-      <c r="H92" t="inlineStr">
+      <c r="H92">
+        <v>0.6975203986837357</v>
+      </c>
+      <c r="I92" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I92">
-        <v>2015</v>
       </c>
       <c r="J92">
         <v>2022</v>
@@ -6142,7 +5704,7 @@
         <v>5460.599999999999</v>
       </c>
       <c r="L92">
-        <v>8632.487444243099</v>
+        <v>4953</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -6155,12 +5717,10 @@
         </is>
       </c>
       <c r="O92">
-        <v>4953</v>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P92">
+        <v>5695.504601895941</v>
       </c>
     </row>
     <row r="93">
@@ -6188,16 +5748,13 @@
           <t>IRQ</t>
         </is>
       </c>
-      <c r="G93">
-        <v>-0.04272087311803473</v>
-      </c>
-      <c r="H93" t="inlineStr">
+      <c r="H93">
+        <v>-0.04322967981494636</v>
+      </c>
+      <c r="I93" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I93">
-        <v>2015</v>
       </c>
       <c r="J93">
         <v>2022</v>
@@ -6206,7 +5763,7 @@
         <v>4413</v>
       </c>
       <c r="L93">
-        <v>7777.055036537001</v>
+        <v>4440</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -6219,12 +5776,10 @@
         </is>
       </c>
       <c r="O93">
-        <v>4440</v>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P93">
+        <v>5110.150032500964</v>
       </c>
     </row>
     <row r="94">
@@ -6252,16 +5807,13 @@
           <t>ISL</t>
         </is>
       </c>
-      <c r="G94">
-        <v>1.648341055915223</v>
-      </c>
-      <c r="H94" t="inlineStr">
+      <c r="H94">
+        <v>1.629162275074634</v>
+      </c>
+      <c r="I94" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I94">
-        <v>2015</v>
       </c>
       <c r="J94">
         <v>2022</v>
@@ -6270,7 +5822,7 @@
         <v>57804.6</v>
       </c>
       <c r="L94">
-        <v>64490.51833905931</v>
+        <v>52951.8</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -6283,12 +5835,10 @@
         </is>
       </c>
       <c r="O94">
-        <v>52951.8</v>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P94">
+        <v>55944.79104200183</v>
       </c>
     </row>
     <row r="95">
@@ -6316,16 +5866,13 @@
           <t>ISR</t>
         </is>
       </c>
-      <c r="G95">
-        <v>2.158761412421703</v>
-      </c>
-      <c r="H95" t="inlineStr">
+      <c r="H95">
+        <v>2.129284912664998</v>
+      </c>
+      <c r="I95" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I95">
-        <v>2015</v>
       </c>
       <c r="J95">
         <v>2022</v>
@@ -6334,7 +5881,7 @@
         <v>42516.6</v>
       </c>
       <c r="L95">
-        <v>48003.82702114557</v>
+        <v>36213</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -6347,12 +5894,10 @@
         </is>
       </c>
       <c r="O95">
-        <v>36213</v>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P95">
+        <v>39144.78225215431</v>
       </c>
     </row>
     <row r="96">
@@ -6380,16 +5925,13 @@
           <t>ITA</t>
         </is>
       </c>
-      <c r="G96">
-        <v>1.174938368473485</v>
-      </c>
-      <c r="H96" t="inlineStr">
+      <c r="H96">
+        <v>1.165360434444316</v>
+      </c>
+      <c r="I96" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I96">
-        <v>2015</v>
       </c>
       <c r="J96">
         <v>2022</v>
@@ -6398,7 +5940,7 @@
         <v>33891.6</v>
       </c>
       <c r="L96">
-        <v>42069.98986452334</v>
+        <v>30639.6</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -6411,12 +5953,10 @@
         </is>
       </c>
       <c r="O96">
-        <v>30639.6</v>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P96">
+        <v>33422.98280484392</v>
       </c>
     </row>
     <row r="97">
@@ -6444,16 +5984,13 @@
           <t>JAM</t>
         </is>
       </c>
-      <c r="G97">
-        <v>0.2093787616340381</v>
-      </c>
-      <c r="H97" t="inlineStr">
+      <c r="H97">
+        <v>0.2118680499575873</v>
+      </c>
+      <c r="I97" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I97">
-        <v>2015</v>
       </c>
       <c r="J97">
         <v>2022</v>
@@ -6462,7 +5999,7 @@
         <v>5215.2</v>
       </c>
       <c r="L97">
-        <v>8814.253066586964</v>
+        <v>5062.8</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -6475,12 +6012,10 @@
         </is>
       </c>
       <c r="O97">
-        <v>5062.8</v>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P97">
+        <v>5820.613927167657</v>
       </c>
     </row>
     <row r="98">
@@ -6508,16 +6043,13 @@
           <t>JOR</t>
         </is>
       </c>
-      <c r="G98">
-        <v>-0.2336094371040076</v>
-      </c>
-      <c r="H98" t="inlineStr">
+      <c r="H98">
+        <v>-0.2363793717214061</v>
+      </c>
+      <c r="I98" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I98">
-        <v>2015</v>
       </c>
       <c r="J98">
         <v>2022</v>
@@ -6526,7 +6058,7 @@
         <v>3909.6</v>
       </c>
       <c r="L98">
-        <v>7107.615339084529</v>
+        <v>4042.8</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -6539,12 +6071,10 @@
         </is>
       </c>
       <c r="O98">
-        <v>4042.8</v>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P98">
+        <v>4655.98993763226</v>
       </c>
     </row>
     <row r="99">
@@ -6572,16 +6102,13 @@
           <t>JPN</t>
         </is>
       </c>
-      <c r="G99">
-        <v>0.4476698457759279</v>
-      </c>
-      <c r="H99" t="inlineStr">
+      <c r="H99">
+        <v>0.4426748608182883</v>
+      </c>
+      <c r="I99" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I99">
-        <v>2015</v>
       </c>
       <c r="J99">
         <v>2022</v>
@@ -6590,7 +6117,7 @@
         <v>36238.2</v>
       </c>
       <c r="L99">
-        <v>46692.0254732579</v>
+        <v>34960.8</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -6603,12 +6130,10 @@
         </is>
       </c>
       <c r="O99">
-        <v>34960.8</v>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P99">
+        <v>37865.12858374525</v>
       </c>
     </row>
     <row r="100">
@@ -6636,16 +6161,13 @@
           <t>KAZ</t>
         </is>
       </c>
-      <c r="G100">
-        <v>0.6202012843066151</v>
-      </c>
-      <c r="H100" t="inlineStr">
+      <c r="H100">
+        <v>0.6263106288014016</v>
+      </c>
+      <c r="I100" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I100">
-        <v>2015</v>
       </c>
       <c r="J100">
         <v>2022</v>
@@ -6654,7 +6176,7 @@
         <v>11058.6</v>
       </c>
       <c r="L100">
-        <v>16822.87464269185</v>
+        <v>10196.4</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
@@ -6667,12 +6189,10 @@
         </is>
       </c>
       <c r="O100">
-        <v>10196.4</v>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P100">
+        <v>11601.20324779545</v>
       </c>
     </row>
     <row r="101">
@@ -6700,16 +6220,13 @@
           <t>KEN</t>
         </is>
       </c>
-      <c r="G101">
-        <v>1.11716249153834</v>
-      </c>
-      <c r="H101" t="inlineStr">
+      <c r="H101">
+        <v>1.126976822818254</v>
+      </c>
+      <c r="I101" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I101">
-        <v>2015</v>
       </c>
       <c r="J101">
         <v>2022</v>
@@ -6718,7 +6235,7 @@
         <v>1747.8</v>
       </c>
       <c r="L101">
-        <v>2649.47931430961</v>
+        <v>1489.2</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -6731,12 +6248,10 @@
         </is>
       </c>
       <c r="O101">
-        <v>1489.2</v>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P101">
+        <v>1716.485995027562</v>
       </c>
     </row>
     <row r="102">
@@ -6764,16 +6279,13 @@
           <t>KGZ</t>
         </is>
       </c>
-      <c r="G102">
-        <v>0.6512276501429913</v>
-      </c>
-      <c r="H102" t="inlineStr">
+      <c r="H102">
+        <v>0.6551790220772286</v>
+      </c>
+      <c r="I102" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I102">
-        <v>2015</v>
       </c>
       <c r="J102">
         <v>2022</v>
@@ -6782,7 +6294,7 @@
         <v>1212</v>
       </c>
       <c r="L102">
-        <v>1956.131849668571</v>
+        <v>1105.8</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -6795,12 +6307,10 @@
         </is>
       </c>
       <c r="O102">
-        <v>1105.8</v>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P102">
+        <v>1272.177825789216</v>
       </c>
     </row>
     <row r="103">
@@ -6828,16 +6338,13 @@
           <t>KHM</t>
         </is>
       </c>
-      <c r="G103">
-        <v>1.823864607249464</v>
-      </c>
-      <c r="H103" t="inlineStr">
+      <c r="H103">
+        <v>1.840867128993811</v>
+      </c>
+      <c r="I103" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I103">
-        <v>2015</v>
       </c>
       <c r="J103">
         <v>2022</v>
@@ -6846,7 +6353,7 @@
         <v>2011.2</v>
       </c>
       <c r="L103">
-        <v>2754.164785436322</v>
+        <v>1547.4</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -6859,12 +6366,10 @@
         </is>
       </c>
       <c r="O103">
-        <v>1547.4</v>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P103">
+        <v>1783.864150899629</v>
       </c>
     </row>
     <row r="104">
@@ -6892,16 +6397,13 @@
           <t>KIR</t>
         </is>
       </c>
-      <c r="G104">
-        <v>1.198314311225849</v>
-      </c>
-      <c r="H104" t="inlineStr">
+      <c r="H104">
+        <v>1.209593230352506</v>
+      </c>
+      <c r="I104" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I104">
-        <v>2015</v>
       </c>
       <c r="J104">
         <v>2022</v>
@@ -6910,7 +6412,7 @@
         <v>1948.2</v>
       </c>
       <c r="L104">
-        <v>2920.063287485893</v>
+        <v>1639.8</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -6923,12 +6425,10 @@
         </is>
       </c>
       <c r="O104">
-        <v>1639.8</v>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P104">
+        <v>1890.798147795817</v>
       </c>
     </row>
     <row r="105">
@@ -6956,16 +6456,13 @@
           <t>KNA</t>
         </is>
       </c>
-      <c r="G105">
-        <v>0.3084197079800869</v>
-      </c>
-      <c r="H105" t="inlineStr">
+      <c r="H105">
+        <v>0.309305518797089</v>
+      </c>
+      <c r="I105" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I105">
-        <v>2015</v>
       </c>
       <c r="J105">
         <v>2022</v>
@@ -6974,7 +6471,7 @@
         <v>21024.6</v>
       </c>
       <c r="L105">
-        <v>30289.53676427126</v>
+        <v>20328.6</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -6987,12 +6484,10 @@
         </is>
       </c>
       <c r="O105">
-        <v>20328.6</v>
-      </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P105">
+        <v>22628.7395716655</v>
       </c>
     </row>
     <row r="106">
@@ -7020,16 +6515,13 @@
           <t>KOR</t>
         </is>
       </c>
-      <c r="G106">
-        <v>1.811287413937147</v>
-      </c>
-      <c r="H106" t="inlineStr">
+      <c r="H106">
+        <v>1.79839520646036</v>
+      </c>
+      <c r="I106" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I106">
-        <v>2015</v>
       </c>
       <c r="J106">
         <v>2022</v>
@@ -7038,7 +6530,7 @@
         <v>33690.6</v>
       </c>
       <c r="L106">
-        <v>39984.95463423663</v>
+        <v>28737.6</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -7051,12 +6543,10 @@
         </is>
       </c>
       <c r="O106">
-        <v>28737.6</v>
-      </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P106">
+        <v>31454.39244112245</v>
       </c>
     </row>
     <row r="107">
@@ -7084,16 +6574,13 @@
           <t>KWT</t>
         </is>
       </c>
-      <c r="G107">
-        <v>-1.254305187477712</v>
-      </c>
-      <c r="H107" t="inlineStr">
+      <c r="H107">
+        <v>-1.249029358963412</v>
+      </c>
+      <c r="I107" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I107">
-        <v>2015</v>
       </c>
       <c r="J107">
         <v>2022</v>
@@ -7102,7 +6589,7 @@
         <v>26580</v>
       </c>
       <c r="L107">
-        <v>41243.86044914411</v>
+        <v>29882.4</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -7115,12 +6602,10 @@
         </is>
       </c>
       <c r="O107">
-        <v>29882.4</v>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P107">
+        <v>32640.27576796474</v>
       </c>
     </row>
     <row r="108">
@@ -7148,16 +6633,13 @@
           <t>LAO</t>
         </is>
       </c>
-      <c r="G108">
-        <v>1.379891808924015</v>
-      </c>
-      <c r="H108" t="inlineStr">
+      <c r="H108">
+        <v>1.394632951828348</v>
+      </c>
+      <c r="I108" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I108">
-        <v>2015</v>
       </c>
       <c r="J108">
         <v>2022</v>
@@ -7166,7 +6648,7 @@
         <v>2589</v>
       </c>
       <c r="L108">
-        <v>3778.050774504504</v>
+        <v>2121</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -7179,12 +6661,10 @@
         </is>
       </c>
       <c r="O108">
-        <v>2121</v>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P108">
+        <v>2446.956995636293</v>
       </c>
     </row>
     <row r="109">
@@ -7212,16 +6692,13 @@
           <t>LBN</t>
         </is>
       </c>
-      <c r="G109">
-        <v>-1.922713545281555</v>
-      </c>
-      <c r="H109" t="inlineStr">
+      <c r="H109">
+        <v>-1.944846250734709</v>
+      </c>
+      <c r="I109" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I109">
-        <v>2015</v>
       </c>
       <c r="J109">
         <v>2022</v>
@@ -7230,7 +6707,7 @@
         <v>5908.8</v>
       </c>
       <c r="L109">
-        <v>13066.52309230542</v>
+        <v>7714.2</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
@@ -7243,12 +6720,10 @@
         </is>
       </c>
       <c r="O109">
-        <v>7714.2</v>
-      </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P109">
+        <v>8822.885862293579</v>
       </c>
     </row>
     <row r="110">
@@ -7276,16 +6751,13 @@
           <t>LBR</t>
         </is>
       </c>
-      <c r="G110">
-        <v>-0.6193373106890964</v>
-      </c>
-      <c r="H110" t="inlineStr">
+      <c r="H110">
+        <v>-0.6180388266924329</v>
+      </c>
+      <c r="I110" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I110">
-        <v>2015</v>
       </c>
       <c r="J110">
         <v>2022</v>
@@ -7294,7 +6766,7 @@
         <v>637.8</v>
       </c>
       <c r="L110">
-        <v>1201.22448438792</v>
+        <v>692.4</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
@@ -7307,12 +6779,10 @@
         </is>
       </c>
       <c r="O110">
-        <v>692.4</v>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P110">
+        <v>792.2297529548127</v>
       </c>
     </row>
     <row r="111">
@@ -7340,16 +6810,13 @@
           <t>LBY</t>
         </is>
       </c>
-      <c r="G111">
-        <v>-0.4522176805501528</v>
-      </c>
-      <c r="H111" t="inlineStr">
+      <c r="H111">
+        <v>-0.4573599600280675</v>
+      </c>
+      <c r="I111" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I111">
-        <v>2015</v>
       </c>
       <c r="J111">
         <v>2022</v>
@@ -7358,7 +6825,7 @@
         <v>7008</v>
       </c>
       <c r="L111">
-        <v>12667.72216185175</v>
+        <v>7458.599999999999</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
@@ -7371,12 +6838,10 @@
         </is>
       </c>
       <c r="O111">
-        <v>7458.599999999999</v>
-      </c>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P111">
+        <v>8535.024260092532</v>
       </c>
     </row>
     <row r="112">
@@ -7404,16 +6869,13 @@
           <t>LCA</t>
         </is>
       </c>
-      <c r="G112">
-        <v>0.6321513997269059</v>
-      </c>
-      <c r="H112" t="inlineStr">
+      <c r="H112">
+        <v>0.6383276020693204</v>
+      </c>
+      <c r="I112" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I112">
-        <v>2015</v>
       </c>
       <c r="J112">
         <v>2022</v>
@@ -7422,7 +6884,7 @@
         <v>11224.2</v>
       </c>
       <c r="L112">
-        <v>17026.58931907186</v>
+        <v>10335</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
@@ -7435,12 +6897,10 @@
         </is>
       </c>
       <c r="O112">
-        <v>10335</v>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P112">
+        <v>11755.42620776551</v>
       </c>
     </row>
     <row r="113">
@@ -7468,6 +6928,9 @@
           <t>LIE</t>
         </is>
       </c>
+      <c r="G113">
+        <v>2015</v>
+      </c>
       <c r="J113">
         <v>2015</v>
       </c>
@@ -7484,14 +6947,6 @@
           <t>GDP per capita (constant 2015 US$)</t>
         </is>
       </c>
-      <c r="P113">
-        <v>2015</v>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>past</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7518,16 +6973,13 @@
           <t>LKA</t>
         </is>
       </c>
-      <c r="G114">
-        <v>-0.04242831277603695</v>
-      </c>
-      <c r="H114" t="inlineStr">
+      <c r="H114">
+        <v>-0.04293184010979952</v>
+      </c>
+      <c r="I114" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I114">
-        <v>2015</v>
       </c>
       <c r="J114">
         <v>2022</v>
@@ -7536,7 +6988,7 @@
         <v>4033.2</v>
       </c>
       <c r="L114">
-        <v>7133.010033431225</v>
+        <v>4057.8</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -7549,12 +7001,10 @@
         </is>
       </c>
       <c r="O114">
-        <v>4057.8</v>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P114">
+        <v>4673.155870288437</v>
       </c>
     </row>
     <row r="115">
@@ -7582,16 +7032,13 @@
           <t>LSO</t>
         </is>
       </c>
-      <c r="G115">
-        <v>-1.054684572456422</v>
-      </c>
-      <c r="H115" t="inlineStr">
+      <c r="H115">
+        <v>-1.059861086060364</v>
+      </c>
+      <c r="I115" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I115">
-        <v>2015</v>
       </c>
       <c r="J115">
         <v>2022</v>
@@ -7600,7 +7047,7 @@
         <v>967.8</v>
       </c>
       <c r="L115">
-        <v>1984.469611075028</v>
+        <v>1121.4</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -7613,12 +7060,10 @@
         </is>
       </c>
       <c r="O115">
-        <v>1121.4</v>
-      </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P115">
+        <v>1290.271596784035</v>
       </c>
     </row>
     <row r="116">
@@ -7646,16 +7091,13 @@
           <t>LTU</t>
         </is>
       </c>
-      <c r="G116">
-        <v>2.369196246030957</v>
-      </c>
-      <c r="H116" t="inlineStr">
+      <c r="H116">
+        <v>2.383746837211569</v>
+      </c>
+      <c r="I116" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I116">
-        <v>2015</v>
       </c>
       <c r="J116">
         <v>2022</v>
@@ -7664,7 +7106,7 @@
         <v>18884.4</v>
       </c>
       <c r="L116">
-        <v>22562.51441706976</v>
+        <v>14269.8</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -7677,12 +7119,10 @@
         </is>
       </c>
       <c r="O116">
-        <v>14269.8</v>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P116">
+        <v>16094.12030997955</v>
       </c>
     </row>
     <row r="117">
@@ -7710,6 +7150,9 @@
           <t>LUX</t>
         </is>
       </c>
+      <c r="G117">
+        <v>2001</v>
+      </c>
       <c r="J117">
         <v>2024</v>
       </c>
@@ -7726,14 +7169,6 @@
           <t>GDP per capita (constant 2015 US$)</t>
         </is>
       </c>
-      <c r="P117">
-        <v>2001</v>
-      </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>past</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7760,16 +7195,13 @@
           <t>LVA</t>
         </is>
       </c>
-      <c r="G118">
-        <v>1.707849929275548</v>
-      </c>
-      <c r="H118" t="inlineStr">
+      <c r="H118">
+        <v>1.720355182756066</v>
+      </c>
+      <c r="I118" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I118">
-        <v>2015</v>
       </c>
       <c r="J118">
         <v>2022</v>
@@ -7778,7 +7210,7 @@
         <v>16405.2</v>
       </c>
       <c r="L118">
-        <v>21270.87521748731</v>
+        <v>13321.8</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -7791,12 +7223,10 @@
         </is>
       </c>
       <c r="O118">
-        <v>13321.8</v>
-      </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P118">
+        <v>15055.76485055632</v>
       </c>
     </row>
     <row r="119">
@@ -7824,16 +7254,13 @@
           <t>MAC</t>
         </is>
       </c>
-      <c r="G119">
-        <v>-12.47874386978006</v>
-      </c>
-      <c r="H119" t="inlineStr">
+      <c r="H119">
+        <v>-12.37127769866471</v>
+      </c>
+      <c r="I119" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I119">
-        <v>2015</v>
       </c>
       <c r="J119">
         <v>2022</v>
@@ -7842,7 +7269,7 @@
         <v>34122</v>
       </c>
       <c r="L119">
-        <v>79562.61168529547</v>
+        <v>70070.39999999999</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -7855,12 +7282,10 @@
         </is>
       </c>
       <c r="O119">
-        <v>70070.39999999999</v>
-      </c>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P119">
+        <v>72560.78437546428</v>
       </c>
     </row>
     <row r="120">
@@ -7888,16 +7313,13 @@
           <t>MAR</t>
         </is>
       </c>
-      <c r="G120">
-        <v>0.3844715592401339</v>
-      </c>
-      <c r="H120" t="inlineStr">
+      <c r="H120">
+        <v>0.3889259887797607</v>
+      </c>
+      <c r="I120" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I120">
-        <v>2015</v>
       </c>
       <c r="J120">
         <v>2022</v>
@@ -7906,7 +7328,7 @@
         <v>3325.8</v>
       </c>
       <c r="L120">
-        <v>5573.547799487184</v>
+        <v>3146.4</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
@@ -7919,12 +7341,10 @@
         </is>
       </c>
       <c r="O120">
-        <v>3146.4</v>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P120">
+        <v>3628.021600545321</v>
       </c>
     </row>
     <row r="121">
@@ -7952,6 +7372,9 @@
           <t>MCO</t>
         </is>
       </c>
+      <c r="G121">
+        <v>1982</v>
+      </c>
       <c r="J121">
         <v>2023</v>
       </c>
@@ -7968,14 +7391,6 @@
           <t>GDP per capita (constant 2015 US$)</t>
         </is>
       </c>
-      <c r="P121">
-        <v>1982</v>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>past</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8002,16 +7417,13 @@
           <t>MDA</t>
         </is>
       </c>
-      <c r="G122">
-        <v>1.890572737876616</v>
-      </c>
-      <c r="H122" t="inlineStr">
+      <c r="H122">
+        <v>1.912350116520502</v>
+      </c>
+      <c r="I122" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I122">
-        <v>2015</v>
       </c>
       <c r="J122">
         <v>2022</v>
@@ -8020,7 +7432,7 @@
         <v>3612</v>
       </c>
       <c r="L122">
-        <v>4884.317703572142</v>
+        <v>2749.8</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
@@ -8033,12 +7445,10 @@
         </is>
       </c>
       <c r="O122">
-        <v>2749.8</v>
-      </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P122">
+        <v>3171.869938298615</v>
       </c>
     </row>
     <row r="123">
@@ -8108,16 +7518,13 @@
           <t>MDV</t>
         </is>
       </c>
-      <c r="G124">
-        <v>0.9572207193699326</v>
-      </c>
-      <c r="H124" t="inlineStr">
+      <c r="H124">
+        <v>0.966818125514156</v>
+      </c>
+      <c r="I124" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I124">
-        <v>2015</v>
       </c>
       <c r="J124">
         <v>2022</v>
@@ -8126,7 +7533,7 @@
         <v>10939.8</v>
       </c>
       <c r="L124">
-        <v>16006.24301389394</v>
+        <v>9645</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
@@ -8139,12 +7546,10 @@
         </is>
       </c>
       <c r="O124">
-        <v>9645</v>
-      </c>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P124">
+        <v>10986.69874954743</v>
       </c>
     </row>
     <row r="125">
@@ -8172,16 +7577,13 @@
           <t>MEX</t>
         </is>
       </c>
-      <c r="G125">
-        <v>-0.005892262481657846</v>
-      </c>
-      <c r="H125" t="inlineStr">
+      <c r="H125">
+        <v>-0.005952063238055416</v>
+      </c>
+      <c r="I125" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I125">
-        <v>2015</v>
       </c>
       <c r="J125">
         <v>2022</v>
@@ -8190,7 +7592,7 @@
         <v>10013.4</v>
       </c>
       <c r="L125">
-        <v>16564.47552801881</v>
+        <v>10021.2</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -8203,12 +7605,10 @@
         </is>
       </c>
       <c r="O125">
-        <v>10021.2</v>
-      </c>
-      <c r="Q125" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P125">
+        <v>11406.11739998089</v>
       </c>
     </row>
     <row r="126">
@@ -8236,16 +7636,13 @@
           <t>MHL</t>
         </is>
       </c>
-      <c r="G126">
-        <v>2.682488884053993</v>
-      </c>
-      <c r="H126" t="inlineStr">
+      <c r="H126">
+        <v>2.71437045103197</v>
+      </c>
+      <c r="I126" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I126">
-        <v>2015</v>
       </c>
       <c r="J126">
         <v>2022</v>
@@ -8254,7 +7651,7 @@
         <v>5517</v>
       </c>
       <c r="L126">
-        <v>6634.652732907707</v>
+        <v>3764.4</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -8267,12 +7664,10 @@
         </is>
       </c>
       <c r="O126">
-        <v>3764.4</v>
-      </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P126">
+        <v>4337.177009205184</v>
       </c>
     </row>
     <row r="127">
@@ -8300,16 +7695,13 @@
           <t>MKD</t>
         </is>
       </c>
-      <c r="G127">
-        <v>1.224019517047164</v>
-      </c>
-      <c r="H127" t="inlineStr">
+      <c r="H127">
+        <v>1.23844799728421</v>
+      </c>
+      <c r="I127" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I127">
-        <v>2015</v>
       </c>
       <c r="J127">
         <v>2022</v>
@@ -8318,7 +7710,7 @@
         <v>6250.8</v>
       </c>
       <c r="L127">
-        <v>9143.816226211684</v>
+        <v>5262.599999999999</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
@@ -8331,12 +7723,10 @@
         </is>
       </c>
       <c r="O127">
-        <v>5262.599999999999</v>
-      </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P127">
+        <v>6048.112051859031</v>
       </c>
     </row>
     <row r="128">
@@ -8364,16 +7754,13 @@
           <t>MLI</t>
         </is>
       </c>
-      <c r="G128">
-        <v>0.3217389341656128</v>
-      </c>
-      <c r="H128" t="inlineStr">
+      <c r="H128">
+        <v>0.3224964904831365</v>
+      </c>
+      <c r="I128" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I128">
-        <v>2015</v>
       </c>
       <c r="J128">
         <v>2022</v>
@@ -8382,7 +7769,7 @@
         <v>876</v>
       </c>
       <c r="L128">
-        <v>1468.340470019767</v>
+        <v>838.1999999999999</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
@@ -8395,12 +7782,10 @@
         </is>
       </c>
       <c r="O128">
-        <v>838.1999999999999</v>
-      </c>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P128">
+        <v>961.6051711616323</v>
       </c>
     </row>
     <row r="129">
@@ -8428,16 +7813,13 @@
           <t>MLT</t>
         </is>
       </c>
-      <c r="G129">
-        <v>2.435822571145926</v>
-      </c>
-      <c r="H129" t="inlineStr">
+      <c r="H129">
+        <v>2.424401941234245</v>
+      </c>
+      <c r="I129" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I129">
-        <v>2015</v>
       </c>
       <c r="J129">
         <v>2022</v>
@@ -8446,7 +7828,7 @@
         <v>31979.4</v>
       </c>
       <c r="L129">
-        <v>36387.95156828655</v>
+        <v>25529.4</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -8459,12 +7841,10 @@
         </is>
       </c>
       <c r="O129">
-        <v>25529.4</v>
-      </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P129">
+        <v>28113.6340724715</v>
       </c>
     </row>
     <row r="130">
@@ -8492,16 +7872,13 @@
           <t>MMR</t>
         </is>
       </c>
-      <c r="G130">
-        <v>0.04726653270473743</v>
-      </c>
-      <c r="H130" t="inlineStr">
+      <c r="H130">
+        <v>0.04755983503552638</v>
+      </c>
+      <c r="I130" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I130">
-        <v>2015</v>
       </c>
       <c r="J130">
         <v>2022</v>
@@ -8510,7 +7887,7 @@
         <v>1174.8</v>
       </c>
       <c r="L130">
-        <v>2067.241978195415</v>
+        <v>1167</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
@@ -8523,12 +7900,10 @@
         </is>
       </c>
       <c r="O130">
-        <v>1167</v>
-      </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P130">
+        <v>1343.153322547399</v>
       </c>
     </row>
     <row r="131">
@@ -8556,16 +7931,13 @@
           <t>MNE</t>
         </is>
       </c>
-      <c r="G131">
-        <v>1.338679204972968</v>
-      </c>
-      <c r="H131" t="inlineStr">
+      <c r="H131">
+        <v>1.353940611304085</v>
+      </c>
+      <c r="I131" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I131">
-        <v>2015</v>
       </c>
       <c r="J131">
         <v>2022</v>
@@ -8574,7 +7946,7 @@
         <v>7808.4</v>
       </c>
       <c r="L131">
-        <v>11137.50836803654</v>
+        <v>6491.4</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -8587,12 +7959,10 @@
         </is>
       </c>
       <c r="O131">
-        <v>6491.4</v>
-      </c>
-      <c r="Q131" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P131">
+        <v>7442.739948136736</v>
       </c>
     </row>
     <row r="132">
@@ -8620,16 +7990,13 @@
           <t>MNG</t>
         </is>
       </c>
-      <c r="G132">
-        <v>0.6372575427812787</v>
-      </c>
-      <c r="H132" t="inlineStr">
+      <c r="H132">
+        <v>0.6448179071053589</v>
+      </c>
+      <c r="I132" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I132">
-        <v>2015</v>
       </c>
       <c r="J132">
         <v>2022</v>
@@ -8638,7 +8005,7 @@
         <v>4206</v>
       </c>
       <c r="L132">
-        <v>6761.352499914909</v>
+        <v>3838.8</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -8651,12 +8018,10 @@
         </is>
       </c>
       <c r="O132">
-        <v>3838.8</v>
-      </c>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P132">
+        <v>4422.416723499616</v>
       </c>
     </row>
     <row r="133">
@@ -8684,16 +8049,13 @@
           <t>MNP</t>
         </is>
       </c>
-      <c r="G133">
-        <v>0.8510656818324865</v>
-      </c>
-      <c r="H133" t="inlineStr">
+      <c r="H133">
+        <v>0.8549959978122063</v>
+      </c>
+      <c r="I133" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I133">
-        <v>2015</v>
       </c>
       <c r="J133">
         <v>2022</v>
@@ -8702,7 +8064,7 @@
         <v>19461.6</v>
       </c>
       <c r="L133">
-        <v>26994.41362942386</v>
+        <v>17665.2</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
@@ -8715,12 +8077,10 @@
         </is>
       </c>
       <c r="O133">
-        <v>17665.2</v>
-      </c>
-      <c r="Q133" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P133">
+        <v>19777.51071669023</v>
       </c>
     </row>
     <row r="134">
@@ -8748,16 +8108,13 @@
           <t>MOZ</t>
         </is>
       </c>
-      <c r="G134">
-        <v>-0.1904558989094076</v>
-      </c>
-      <c r="H134" t="inlineStr">
+      <c r="H134">
+        <v>-0.1896529426714295</v>
+      </c>
+      <c r="I134" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I134">
-        <v>2015</v>
       </c>
       <c r="J134">
         <v>2022</v>
@@ -8766,7 +8123,7 @@
         <v>595.8</v>
       </c>
       <c r="L134">
-        <v>1051.308786074829</v>
+        <v>610.8</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
@@ -8779,12 +8136,10 @@
         </is>
       </c>
       <c r="O134">
-        <v>610.8</v>
-      </c>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P134">
+        <v>697.3864977258478</v>
       </c>
     </row>
     <row r="135">
@@ -8812,16 +8167,13 @@
           <t>MRT</t>
         </is>
       </c>
-      <c r="G135">
-        <v>0.09633990760119104</v>
-      </c>
-      <c r="H135" t="inlineStr">
+      <c r="H135">
+        <v>0.0971673857427829</v>
+      </c>
+      <c r="I135" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I135">
-        <v>2015</v>
       </c>
       <c r="J135">
         <v>2022</v>
@@ -8830,7 +8182,7 @@
         <v>1576.8</v>
       </c>
       <c r="L135">
-        <v>2768.183744714439</v>
+        <v>1555.2</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -8843,12 +8195,10 @@
         </is>
       </c>
       <c r="O135">
-        <v>1555.2</v>
-      </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P135">
+        <v>1792.892998637411</v>
       </c>
     </row>
     <row r="136">
@@ -8876,16 +8226,13 @@
           <t>MUS</t>
         </is>
       </c>
-      <c r="G136">
-        <v>0.7888926824338195</v>
-      </c>
-      <c r="H136" t="inlineStr">
+      <c r="H136">
+        <v>0.7969067036432956</v>
+      </c>
+      <c r="I136" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I136">
-        <v>2015</v>
       </c>
       <c r="J136">
         <v>2022</v>
@@ -8894,7 +8241,7 @@
         <v>10552.2</v>
       </c>
       <c r="L136">
-        <v>15801.19990216533</v>
+        <v>9507.6</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
@@ -8907,12 +8254,10 @@
         </is>
       </c>
       <c r="O136">
-        <v>9507.6</v>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P136">
+        <v>10833.33732236374</v>
       </c>
     </row>
     <row r="137">
@@ -8940,16 +8285,13 @@
           <t>MWI</t>
         </is>
       </c>
-      <c r="G137">
-        <v>0.2976119786140267</v>
-      </c>
-      <c r="H137" t="inlineStr">
+      <c r="H137">
+        <v>0.2956656903324252</v>
+      </c>
+      <c r="I137" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I137">
-        <v>2015</v>
       </c>
       <c r="J137">
         <v>2022</v>
@@ -8958,7 +8300,7 @@
         <v>560.4</v>
       </c>
       <c r="L137">
-        <v>919.8860466708097</v>
+        <v>539.4</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
@@ -8971,12 +8313,10 @@
         </is>
       </c>
       <c r="O137">
-        <v>539.4</v>
-      </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P137">
+        <v>614.3687409869491</v>
       </c>
     </row>
     <row r="138">
@@ -9004,16 +8344,13 @@
           <t>MYS</t>
         </is>
       </c>
-      <c r="G138">
-        <v>1.117665780330412</v>
-      </c>
-      <c r="H138" t="inlineStr">
+      <c r="H138">
+        <v>1.128804682375947</v>
+      </c>
+      <c r="I138" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I138">
-        <v>2015</v>
       </c>
       <c r="J138">
         <v>2022</v>
@@ -9022,7 +8359,7 @@
         <v>11174.4</v>
       </c>
       <c r="L138">
-        <v>16011.60704890362</v>
+        <v>9648.6</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -9035,12 +8372,10 @@
         </is>
       </c>
       <c r="O138">
-        <v>9648.6</v>
-      </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P138">
+        <v>10990.71562931548</v>
       </c>
     </row>
     <row r="139">
@@ -9068,16 +8403,13 @@
           <t>NAM</t>
         </is>
       </c>
-      <c r="G139">
-        <v>-1.405481628600882</v>
-      </c>
-      <c r="H139" t="inlineStr">
+      <c r="H139">
+        <v>-1.422201182565589</v>
+      </c>
+      <c r="I139" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I139">
-        <v>2015</v>
       </c>
       <c r="J139">
         <v>2022</v>
@@ -9086,7 +8418,7 @@
         <v>3905.4</v>
       </c>
       <c r="L139">
-        <v>8335.501003506075</v>
+        <v>4774.2</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
@@ -9099,12 +8431,10 @@
         </is>
       </c>
       <c r="O139">
-        <v>4774.2</v>
-      </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P139">
+        <v>5491.640927630626</v>
       </c>
     </row>
     <row r="140">
@@ -9174,16 +8504,13 @@
           <t>NER</t>
         </is>
       </c>
-      <c r="G141">
-        <v>1.22265378686221</v>
-      </c>
-      <c r="H141" t="inlineStr">
+      <c r="H141">
+        <v>1.213037072536979</v>
+      </c>
+      <c r="I141" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I141">
-        <v>2015</v>
       </c>
       <c r="J141">
         <v>2022</v>
@@ -9192,7 +8519,7 @@
         <v>567</v>
       </c>
       <c r="L141">
-        <v>820.3384685300509</v>
+        <v>485.4</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
@@ -9205,12 +8532,10 @@
         </is>
       </c>
       <c r="O141">
-        <v>485.4</v>
-      </c>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P141">
+        <v>551.5659651753168</v>
       </c>
     </row>
     <row r="142">
@@ -9238,16 +8563,13 @@
           <t>NGA</t>
         </is>
       </c>
-      <c r="G142">
-        <v>-0.5198604821955745</v>
-      </c>
-      <c r="H142" t="inlineStr">
+      <c r="H142">
+        <v>-0.5255296063603428</v>
+      </c>
+      <c r="I142" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I142">
-        <v>2015</v>
       </c>
       <c r="J142">
         <v>2022</v>
@@ -9256,7 +8578,7 @@
         <v>2398.8</v>
       </c>
       <c r="L142">
-        <v>4597.745939227701</v>
+        <v>2586</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
@@ -9269,12 +8591,10 @@
         </is>
       </c>
       <c r="O142">
-        <v>2586</v>
-      </c>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P142">
+        <v>2983.23290724208</v>
       </c>
     </row>
     <row r="143">
@@ -9302,16 +8622,13 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G143">
-        <v>0.3306229817637489</v>
-      </c>
-      <c r="H143" t="inlineStr">
+      <c r="H143">
+        <v>0.3340263113748238</v>
+      </c>
+      <c r="I143" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I143">
-        <v>2015</v>
       </c>
       <c r="J143">
         <v>2022</v>
@@ -9320,7 +8637,7 @@
         <v>2175.6</v>
       </c>
       <c r="L143">
-        <v>3695.042835559436</v>
+        <v>2074.2</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -9333,12 +8650,10 @@
         </is>
       </c>
       <c r="O143">
-        <v>2074.2</v>
-      </c>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P143">
+        <v>2392.920156532266</v>
       </c>
     </row>
     <row r="144">
@@ -9366,16 +8681,13 @@
           <t>NLD</t>
         </is>
       </c>
-      <c r="G144">
-        <v>2.003360838403109</v>
-      </c>
-      <c r="H144" t="inlineStr">
+      <c r="H144">
+        <v>1.973108287728418</v>
+      </c>
+      <c r="I144" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I144">
-        <v>2015</v>
       </c>
       <c r="J144">
         <v>2022</v>
@@ -9384,7 +8696,7 @@
         <v>51777.6</v>
       </c>
       <c r="L144">
-        <v>57669.44004109632</v>
+        <v>45793.8</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
@@ -9397,12 +8709,10 @@
         </is>
       </c>
       <c r="O144">
-        <v>45793.8</v>
-      </c>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P144">
+        <v>48829.1286913642</v>
       </c>
     </row>
     <row r="145">
@@ -9430,16 +8740,13 @@
           <t>NOR</t>
         </is>
       </c>
-      <c r="G145">
-        <v>2.120354755975167</v>
-      </c>
-      <c r="H145" t="inlineStr">
+      <c r="H145">
+        <v>2.20934609613626</v>
+      </c>
+      <c r="I145" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I145">
-        <v>2015</v>
       </c>
       <c r="J145">
         <v>2022</v>
@@ -9448,7 +8755,7 @@
         <v>79620</v>
       </c>
       <c r="L145">
-        <v>83453.84039285962</v>
+        <v>74809.8</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
@@ -9461,12 +8768,10 @@
         </is>
       </c>
       <c r="O145">
-        <v>74809.8</v>
-      </c>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P145">
+        <v>77063.79390952511</v>
       </c>
     </row>
     <row r="146">
@@ -9494,16 +8799,13 @@
           <t>NPL</t>
         </is>
       </c>
-      <c r="G146">
-        <v>1.731520943522932</v>
-      </c>
-      <c r="H146" t="inlineStr">
+      <c r="H146">
+        <v>1.738851395902543</v>
+      </c>
+      <c r="I146" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I146">
-        <v>2015</v>
       </c>
       <c r="J146">
         <v>2022</v>
@@ -9512,7 +8814,7 @@
         <v>1113.6</v>
       </c>
       <c r="L146">
-        <v>1536.340888828112</v>
+        <v>875.4</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
@@ -9525,12 +8827,10 @@
         </is>
       </c>
       <c r="O146">
-        <v>875.4</v>
-      </c>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P146">
+        <v>1004.801954049226</v>
       </c>
     </row>
     <row r="147">
@@ -9558,16 +8858,13 @@
           <t>NRU</t>
         </is>
       </c>
-      <c r="G147">
-        <v>0.688768284834554</v>
-      </c>
-      <c r="H147" t="inlineStr">
+      <c r="H147">
+        <v>0.6963786466182447</v>
+      </c>
+      <c r="I147" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I147">
-        <v>2015</v>
       </c>
       <c r="J147">
         <v>2022</v>
@@ -9576,7 +8873,7 @@
         <v>8460.6</v>
       </c>
       <c r="L147">
-        <v>13049.71888962598</v>
+        <v>7703.4</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
@@ -9589,12 +8886,10 @@
         </is>
       </c>
       <c r="O147">
-        <v>7703.4</v>
-      </c>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P147">
+        <v>8810.729212511051</v>
       </c>
     </row>
     <row r="148">
@@ -9622,16 +8917,13 @@
           <t>NZL</t>
         </is>
       </c>
-      <c r="G148">
-        <v>1.361376967729354</v>
-      </c>
-      <c r="H148" t="inlineStr">
+      <c r="H148">
+        <v>1.34178108454883</v>
+      </c>
+      <c r="I148" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I148">
-        <v>2015</v>
       </c>
       <c r="J148">
         <v>2022</v>
@@ -9640,7 +8932,7 @@
         <v>42667.8</v>
       </c>
       <c r="L148">
-        <v>50539.13375987604</v>
+        <v>38665.2</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
@@ -9653,12 +8945,10 @@
         </is>
       </c>
       <c r="O148">
-        <v>38665.2</v>
-      </c>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P148">
+        <v>41641.23797452403</v>
       </c>
     </row>
     <row r="149">
@@ -9686,16 +8976,13 @@
           <t>OMN</t>
         </is>
       </c>
-      <c r="G149">
-        <v>-0.007326452131297044</v>
-      </c>
-      <c r="H149" t="inlineStr">
+      <c r="H149">
+        <v>-0.007358897943699308</v>
+      </c>
+      <c r="I149" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I149">
-        <v>2015</v>
       </c>
       <c r="J149">
         <v>2022</v>
@@ -9704,7 +8991,7 @@
         <v>18792.6</v>
       </c>
       <c r="L149">
-        <v>28425.78132670491</v>
+        <v>18808.2</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
@@ -9717,12 +9004,10 @@
         </is>
       </c>
       <c r="O149">
-        <v>18808.2</v>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P149">
+        <v>21005.09195912609</v>
       </c>
     </row>
     <row r="150">
@@ -9750,16 +9035,13 @@
           <t>PAK</t>
         </is>
       </c>
-      <c r="G150">
-        <v>1.214087850475551</v>
-      </c>
-      <c r="H150" t="inlineStr">
+      <c r="H150">
+        <v>1.224172995847872</v>
+      </c>
+      <c r="I150" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I150">
-        <v>2015</v>
       </c>
       <c r="J150">
         <v>2022</v>
@@ -9768,7 +9050,7 @@
         <v>1642.2</v>
       </c>
       <c r="L150">
-        <v>2453.741733106034</v>
+        <v>1380.6</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
@@ -9781,12 +9063,10 @@
         </is>
       </c>
       <c r="O150">
-        <v>1380.6</v>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P150">
+        <v>1590.712974993387</v>
       </c>
     </row>
     <row r="151">
@@ -9814,16 +9094,13 @@
           <t>PAN</t>
         </is>
       </c>
-      <c r="G151">
-        <v>1.007532547208882</v>
-      </c>
-      <c r="H151" t="inlineStr">
+      <c r="H151">
+        <v>1.014808494574083</v>
+      </c>
+      <c r="I151" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I151">
-        <v>2015</v>
       </c>
       <c r="J151">
         <v>2022</v>
@@ -9832,7 +9109,7 @@
         <v>15917.4</v>
       </c>
       <c r="L151">
-        <v>22309.46414802766</v>
+        <v>14082.6</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -9845,12 +9122,10 @@
         </is>
       </c>
       <c r="O151">
-        <v>14082.6</v>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P151">
+        <v>15889.42492735167</v>
       </c>
     </row>
     <row r="152">
@@ -9878,16 +9153,13 @@
           <t>PER</t>
         </is>
       </c>
-      <c r="G152">
-        <v>0.4856848627847877</v>
-      </c>
-      <c r="H152" t="inlineStr">
+      <c r="H152">
+        <v>0.49132849129962</v>
+      </c>
+      <c r="I152" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I152">
-        <v>2015</v>
       </c>
       <c r="J152">
         <v>2022</v>
@@ -9896,7 +9168,7 @@
         <v>6667.8</v>
       </c>
       <c r="L152">
-        <v>10720.6829231845</v>
+        <v>6231.599999999999</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
@@ -9909,12 +9181,10 @@
         </is>
       </c>
       <c r="O152">
-        <v>6231.599999999999</v>
-      </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P152">
+        <v>7148.52626917465</v>
       </c>
     </row>
     <row r="153">
@@ -9942,16 +9212,13 @@
           <t>PHL</t>
         </is>
       </c>
-      <c r="G153">
-        <v>1.432551477239668</v>
-      </c>
-      <c r="H153" t="inlineStr">
+      <c r="H153">
+        <v>1.449128821765035</v>
+      </c>
+      <c r="I153" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I153">
-        <v>2015</v>
       </c>
       <c r="J153">
         <v>2022</v>
@@ -9960,7 +9227,7 @@
         <v>3577.8</v>
       </c>
       <c r="L153">
-        <v>5163.50692494636</v>
+        <v>2910</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
@@ -9973,12 +9240,10 @@
         </is>
       </c>
       <c r="O153">
-        <v>2910</v>
-      </c>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P153">
+        <v>3356.223998929207</v>
       </c>
     </row>
     <row r="154">
@@ -10006,16 +9271,13 @@
           <t>PLW</t>
         </is>
       </c>
-      <c r="G154">
-        <v>-2.07590559869865</v>
-      </c>
-      <c r="H154" t="inlineStr">
+      <c r="H154">
+        <v>-2.092412656689622</v>
+      </c>
+      <c r="I154" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I154">
-        <v>2015</v>
       </c>
       <c r="J154">
         <v>2022</v>
@@ -10024,7 +9286,7 @@
         <v>12129.6</v>
       </c>
       <c r="L154">
-        <v>24452.23933328762</v>
+        <v>15690.6</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -10037,12 +9299,10 @@
         </is>
       </c>
       <c r="O154">
-        <v>15690.6</v>
-      </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P154">
+        <v>17642.17202220441</v>
       </c>
     </row>
     <row r="155">
@@ -10070,16 +9330,13 @@
           <t>PNG</t>
         </is>
       </c>
-      <c r="G155">
-        <v>-0.04861938473104845</v>
-      </c>
-      <c r="H155" t="inlineStr">
+      <c r="H155">
+        <v>-0.04914876997734398</v>
+      </c>
+      <c r="I155" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I155">
-        <v>2015</v>
       </c>
       <c r="J155">
         <v>2022</v>
@@ -10088,7 +9345,7 @@
         <v>2467.2</v>
       </c>
       <c r="L155">
-        <v>4419.779169031128</v>
+        <v>2484.6</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
@@ -10101,12 +9358,10 @@
         </is>
       </c>
       <c r="O155">
-        <v>2484.6</v>
-      </c>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P155">
+        <v>2866.387446171577</v>
       </c>
     </row>
     <row r="156">
@@ -10134,16 +9389,13 @@
           <t>POL</t>
         </is>
       </c>
-      <c r="G156">
-        <v>2.580184180099017</v>
-      </c>
-      <c r="H156" t="inlineStr">
+      <c r="H156">
+        <v>2.59893726499841</v>
+      </c>
+      <c r="I156" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I156">
-        <v>2015</v>
       </c>
       <c r="J156">
         <v>2022</v>
@@ -10152,7 +9404,7 @@
         <v>17303.4</v>
       </c>
       <c r="L156">
-        <v>20322.82858916911</v>
+        <v>12637.8</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
@@ -10165,12 +9417,10 @@
         </is>
       </c>
       <c r="O156">
-        <v>12637.8</v>
-      </c>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P156">
+        <v>14303.84435772418</v>
       </c>
     </row>
     <row r="157">
@@ -10198,16 +9448,13 @@
           <t>PRI</t>
         </is>
       </c>
-      <c r="G157">
-        <v>0.1498401719781879</v>
-      </c>
-      <c r="H157" t="inlineStr">
+      <c r="H157">
+        <v>0.1490291252232916</v>
+      </c>
+      <c r="I157" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I157">
-        <v>2015</v>
       </c>
       <c r="J157">
         <v>2022</v>
@@ -10216,7 +9463,7 @@
         <v>29643.6</v>
       </c>
       <c r="L157">
-        <v>40541.3459030017</v>
+        <v>29242.2</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -10229,12 +9476,10 @@
         </is>
       </c>
       <c r="O157">
-        <v>29242.2</v>
-      </c>
-      <c r="Q157" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P157">
+        <v>31977.47851089056</v>
       </c>
     </row>
     <row r="158">
@@ -10262,16 +9507,13 @@
           <t>PRT</t>
         </is>
       </c>
-      <c r="G158">
-        <v>1.255885903045144</v>
-      </c>
-      <c r="H158" t="inlineStr">
+      <c r="H158">
+        <v>1.259551208994302</v>
+      </c>
+      <c r="I158" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I158">
-        <v>2015</v>
       </c>
       <c r="J158">
         <v>2022</v>
@@ -10280,7 +9522,7 @@
         <v>22042.8</v>
       </c>
       <c r="L158">
-        <v>28929.48541082762</v>
+        <v>19215.6</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
@@ -10293,12 +9535,10 @@
         </is>
       </c>
       <c r="O158">
-        <v>19215.6</v>
-      </c>
-      <c r="Q158" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P158">
+        <v>21441.17153781515</v>
       </c>
     </row>
     <row r="159">
@@ -10326,16 +9566,13 @@
           <t>PRY</t>
         </is>
       </c>
-      <c r="G159">
-        <v>0.4002856043602045</v>
-      </c>
-      <c r="H159" t="inlineStr">
+      <c r="H159">
+        <v>0.40497942693377</v>
+      </c>
+      <c r="I159" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I159">
-        <v>2015</v>
       </c>
       <c r="J159">
         <v>2022</v>
@@ -10344,7 +9581,7 @@
         <v>6218.4</v>
       </c>
       <c r="L159">
-        <v>10151.62092906432</v>
+        <v>5879.4</v>
       </c>
       <c r="M159" t="inlineStr">
         <is>
@@ -10357,12 +9594,10 @@
         </is>
       </c>
       <c r="O159">
-        <v>5879.4</v>
-      </c>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P159">
+        <v>6749.119880907318</v>
       </c>
     </row>
     <row r="160">
@@ -10390,16 +9625,13 @@
           <t>PSE</t>
         </is>
       </c>
-      <c r="G160">
-        <v>-0.3746984486148831</v>
-      </c>
-      <c r="H160" t="inlineStr">
+      <c r="H160">
+        <v>-0.3790275658022892</v>
+      </c>
+      <c r="I160" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I160">
-        <v>2015</v>
       </c>
       <c r="J160">
         <v>2022</v>
@@ -10408,7 +9640,7 @@
         <v>3100.2</v>
       </c>
       <c r="L160">
-        <v>5791.155538749073</v>
+        <v>3272.4</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
@@ -10421,12 +9653,10 @@
         </is>
       </c>
       <c r="O160">
-        <v>3272.4</v>
-      </c>
-      <c r="Q160" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P160">
+        <v>3772.76856491895</v>
       </c>
     </row>
     <row r="161">
@@ -10454,16 +9684,13 @@
           <t>PYF</t>
         </is>
       </c>
-      <c r="G161">
-        <v>0.8354845093404363</v>
-      </c>
-      <c r="H161" t="inlineStr">
+      <c r="H161">
+        <v>0.838300359853138</v>
+      </c>
+      <c r="I161" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I161">
-        <v>2015</v>
       </c>
       <c r="J161">
         <v>2022</v>
@@ -10472,7 +9699,7 @@
         <v>21019.8</v>
       </c>
       <c r="L161">
-        <v>28869.56823985415</v>
+        <v>19167</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
@@ -10485,12 +9712,10 @@
         </is>
       </c>
       <c r="O161">
-        <v>19167</v>
-      </c>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P161">
+        <v>21389.19004892461</v>
       </c>
     </row>
     <row r="162">
@@ -10518,16 +9743,13 @@
           <t>QAT</t>
         </is>
       </c>
-      <c r="G162">
-        <v>-1.730981638371507</v>
-      </c>
-      <c r="H162" t="inlineStr">
+      <c r="H162">
+        <v>-1.739551573475995</v>
+      </c>
+      <c r="I162" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I162">
-        <v>2015</v>
       </c>
       <c r="J162">
         <v>2022</v>
@@ -10536,7 +9758,7 @@
         <v>64315.8</v>
       </c>
       <c r="L162">
-        <v>78655.13805574451</v>
+        <v>68985</v>
       </c>
       <c r="M162" t="inlineStr">
         <is>
@@ -10549,12 +9771,10 @@
         </is>
       </c>
       <c r="O162">
-        <v>68985</v>
-      </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P162">
+        <v>71523.6795767468</v>
       </c>
     </row>
     <row r="163">
@@ -10582,16 +9802,13 @@
           <t>ROU</t>
         </is>
       </c>
-      <c r="G163">
-        <v>2.284983890506299</v>
-      </c>
-      <c r="H163" t="inlineStr">
+      <c r="H163">
+        <v>2.307627902772737</v>
+      </c>
+      <c r="I163" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I163">
-        <v>2015</v>
       </c>
       <c r="J163">
         <v>2022</v>
@@ -10600,7 +9817,7 @@
         <v>12114.6</v>
       </c>
       <c r="L163">
-        <v>15003.79255750503</v>
+        <v>8977.199999999999</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
@@ -10613,12 +9830,10 @@
         </is>
       </c>
       <c r="O163">
-        <v>8977.199999999999</v>
-      </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P163">
+        <v>10240.43251076608</v>
       </c>
     </row>
     <row r="164">
@@ -10646,16 +9861,13 @@
           <t>RUS</t>
         </is>
       </c>
-      <c r="G164">
-        <v>0.6534309249127789</v>
-      </c>
-      <c r="H164" t="inlineStr">
+      <c r="H164">
+        <v>0.6601757147650866</v>
+      </c>
+      <c r="I164" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I164">
-        <v>2015</v>
       </c>
       <c r="J164">
         <v>2022</v>
@@ -10664,7 +9876,7 @@
         <v>10119</v>
       </c>
       <c r="L164">
-        <v>15456.86939435468</v>
+        <v>9277.799999999999</v>
       </c>
       <c r="M164" t="inlineStr">
         <is>
@@ -10677,12 +9889,10 @@
         </is>
       </c>
       <c r="O164">
-        <v>9277.799999999999</v>
-      </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P164">
+        <v>10576.63008176679</v>
       </c>
     </row>
     <row r="165">
@@ -10710,16 +9920,13 @@
           <t>RWA</t>
         </is>
       </c>
-      <c r="G165">
-        <v>1.879191055063558</v>
-      </c>
-      <c r="H165" t="inlineStr">
+      <c r="H165">
+        <v>1.88274813836473</v>
+      </c>
+      <c r="I165" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I165">
-        <v>2015</v>
       </c>
       <c r="J165">
         <v>2022</v>
@@ -10728,7 +9935,7 @@
         <v>948.5999999999999</v>
       </c>
       <c r="L165">
-        <v>1277.169440588012</v>
+        <v>733.8</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
@@ -10741,12 +9948,10 @@
         </is>
       </c>
       <c r="O165">
-        <v>733.8</v>
-      </c>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P165">
+        <v>840.3356242515423</v>
       </c>
     </row>
     <row r="166">
@@ -10774,16 +9979,13 @@
           <t>SAU</t>
         </is>
       </c>
-      <c r="G166">
-        <v>1.384281227324168</v>
-      </c>
-      <c r="H166" t="inlineStr">
+      <c r="H166">
+        <v>1.38283294699696</v>
+      </c>
+      <c r="I166" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I166">
-        <v>2015</v>
       </c>
       <c r="J166">
         <v>2022</v>
@@ -10792,7 +9994,7 @@
         <v>26707.2</v>
       </c>
       <c r="L166">
-        <v>33768.49332514644</v>
+        <v>23256</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
@@ -10805,12 +10007,10 @@
         </is>
       </c>
       <c r="O166">
-        <v>23256</v>
-      </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P166">
+        <v>25727.99982030786</v>
       </c>
     </row>
     <row r="167">
@@ -10838,16 +10038,13 @@
           <t>SDN</t>
         </is>
       </c>
-      <c r="G167">
-        <v>-2.01983103544427</v>
-      </c>
-      <c r="H167" t="inlineStr">
+      <c r="H167">
+        <v>-2.031322104976283</v>
+      </c>
+      <c r="I167" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I167">
-        <v>2015</v>
       </c>
       <c r="J167">
         <v>2022</v>
@@ -10856,7 +10053,7 @@
         <v>973.1999999999999</v>
       </c>
       <c r="L167">
-        <v>2294.3907763349</v>
+        <v>1292.4</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
@@ -10869,12 +10066,10 @@
         </is>
       </c>
       <c r="O167">
-        <v>1292.4</v>
-      </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P167">
+        <v>1488.519175050042</v>
       </c>
     </row>
     <row r="168">
@@ -10902,16 +10097,13 @@
           <t>SEN</t>
         </is>
       </c>
-      <c r="G168">
-        <v>1.146837975324035</v>
-      </c>
-      <c r="H168" t="inlineStr">
+      <c r="H168">
+        <v>1.155189557636232</v>
+      </c>
+      <c r="I168" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I168">
-        <v>2015</v>
       </c>
       <c r="J168">
         <v>2022</v>
@@ -10920,7 +10112,7 @@
         <v>1433.4</v>
       </c>
       <c r="L168">
-        <v>2159.70627446709</v>
+        <v>1218</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
@@ -10933,12 +10125,10 @@
         </is>
       </c>
       <c r="O168">
-        <v>1218</v>
-      </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P168">
+        <v>1402.28341571494</v>
       </c>
     </row>
     <row r="169">
@@ -10966,16 +10156,13 @@
           <t>SGP</t>
         </is>
       </c>
-      <c r="G169">
-        <v>4.466128451967109</v>
-      </c>
-      <c r="H169" t="inlineStr">
+      <c r="H169">
+        <v>4.452459145681563</v>
+      </c>
+      <c r="I169" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I169">
-        <v>2015</v>
       </c>
       <c r="J169">
         <v>2022</v>
@@ -10984,7 +10171,7 @@
         <v>68218.8</v>
       </c>
       <c r="L169">
-        <v>66974.72212000185</v>
+        <v>55645.8</v>
       </c>
       <c r="M169" t="inlineStr">
         <is>
@@ -10997,12 +10184,10 @@
         </is>
       </c>
       <c r="O169">
-        <v>55645.8</v>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P169">
+        <v>58596.85987772482</v>
       </c>
     </row>
     <row r="170">
@@ -11030,16 +10215,13 @@
           <t>SLB</t>
         </is>
       </c>
-      <c r="G170">
-        <v>-0.3934017743878217</v>
-      </c>
-      <c r="H170" t="inlineStr">
+      <c r="H170">
+        <v>-0.3973291976682682</v>
+      </c>
+      <c r="I170" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I170">
-        <v>2015</v>
       </c>
       <c r="J170">
         <v>2022</v>
@@ -11048,7 +10230,7 @@
         <v>1932.6</v>
       </c>
       <c r="L170">
-        <v>3643.914293648281</v>
+        <v>2045.4</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
@@ -11061,12 +10243,10 @@
         </is>
       </c>
       <c r="O170">
-        <v>2045.4</v>
-      </c>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P170">
+        <v>2359.660989782509</v>
       </c>
     </row>
     <row r="171">
@@ -11094,16 +10274,13 @@
           <t>SLE</t>
         </is>
       </c>
-      <c r="G171">
-        <v>0.7890787556807847</v>
-      </c>
-      <c r="H171" t="inlineStr">
+      <c r="H171">
+        <v>0.7927518819164691</v>
+      </c>
+      <c r="I171" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I171">
-        <v>2015</v>
       </c>
       <c r="J171">
         <v>2022</v>
@@ -11112,7 +10289,7 @@
         <v>1077</v>
       </c>
       <c r="L171">
-        <v>1699.509163813855</v>
+        <v>964.8</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
@@ -11125,12 +10302,10 @@
         </is>
       </c>
       <c r="O171">
-        <v>964.8</v>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P171">
+        <v>1108.582429724299</v>
       </c>
     </row>
     <row r="172">
@@ -11158,16 +10333,13 @@
           <t>SLV</t>
         </is>
       </c>
-      <c r="G172">
-        <v>0.9710346571457527</v>
-      </c>
-      <c r="H172" t="inlineStr">
+      <c r="H172">
+        <v>0.9825603968661483</v>
+      </c>
+      <c r="I172" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I172">
-        <v>2015</v>
       </c>
       <c r="J172">
         <v>2022</v>
@@ -11176,7 +10348,7 @@
         <v>4356</v>
       </c>
       <c r="L172">
-        <v>6678.61420914045</v>
+        <v>3790.2</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -11189,12 +10361,10 @@
         </is>
       </c>
       <c r="O172">
-        <v>3790.2</v>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P172">
+        <v>4366.739332093423</v>
       </c>
     </row>
     <row r="173">
@@ -11222,16 +10392,13 @@
           <t>SMR</t>
         </is>
       </c>
-      <c r="G173">
-        <v>2.724571188573325</v>
-      </c>
-      <c r="H173" t="inlineStr">
+      <c r="H173">
+        <v>2.682941639988412</v>
+      </c>
+      <c r="I173" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I173">
-        <v>2015</v>
       </c>
       <c r="J173">
         <v>2022</v>
@@ -11240,7 +10407,7 @@
         <v>51277.2</v>
       </c>
       <c r="L173">
-        <v>55062.20861011148</v>
+        <v>43146.6</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -11253,12 +10420,10 @@
         </is>
       </c>
       <c r="O173">
-        <v>43146.6</v>
-      </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P173">
+        <v>46171.84436787879</v>
       </c>
     </row>
     <row r="174">
@@ -11328,16 +10493,13 @@
           <t>SRB</t>
         </is>
       </c>
-      <c r="G175">
-        <v>2.164577470593437</v>
-      </c>
-      <c r="H175" t="inlineStr">
+      <c r="H175">
+        <v>2.189475577369864</v>
+      </c>
+      <c r="I175" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I175">
-        <v>2015</v>
       </c>
       <c r="J175">
         <v>2022</v>
@@ -11346,7 +10508,7 @@
         <v>7857.599999999999</v>
       </c>
       <c r="L175">
-        <v>10056.16500818091</v>
+        <v>5820.599999999999</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -11359,12 +10521,10 @@
         </is>
       </c>
       <c r="O175">
-        <v>5820.599999999999</v>
-      </c>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P175">
+        <v>6682.376687874672</v>
       </c>
     </row>
     <row r="176">
@@ -11434,16 +10594,13 @@
           <t>STP</t>
         </is>
       </c>
-      <c r="G177">
-        <v>0.5469865871471841</v>
-      </c>
-      <c r="H177" t="inlineStr">
+      <c r="H177">
+        <v>0.5510730522400016</v>
+      </c>
+      <c r="I177" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I177">
-        <v>2015</v>
       </c>
       <c r="J177">
         <v>2022</v>
@@ -11452,7 +10609,7 @@
         <v>1403.4</v>
       </c>
       <c r="L177">
-        <v>2305.242192439806</v>
+        <v>1298.4</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
@@ -11465,12 +10622,10 @@
         </is>
       </c>
       <c r="O177">
-        <v>1298.4</v>
-      </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P177">
+        <v>1495.472422490672</v>
       </c>
     </row>
     <row r="178">
@@ -11498,16 +10653,13 @@
           <t>SUR</t>
         </is>
       </c>
-      <c r="G178">
-        <v>-1.603928758121336</v>
-      </c>
-      <c r="H178" t="inlineStr">
+      <c r="H178">
+        <v>-1.621741715714575</v>
+      </c>
+      <c r="I178" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I178">
-        <v>2015</v>
       </c>
       <c r="J178">
         <v>2022</v>
@@ -11516,7 +10668,7 @@
         <v>7081.2</v>
       </c>
       <c r="L178">
-        <v>14755.62786186215</v>
+        <v>8813.4</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
@@ -11529,12 +10681,10 @@
         </is>
       </c>
       <c r="O178">
-        <v>8813.4</v>
-      </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P178">
+        <v>10057.04359029497</v>
       </c>
     </row>
     <row r="179">
@@ -11562,16 +10712,13 @@
           <t>SVK</t>
         </is>
       </c>
-      <c r="G179">
-        <v>1.228023634154559</v>
-      </c>
-      <c r="H179" t="inlineStr">
+      <c r="H179">
+        <v>1.234522769257491</v>
+      </c>
+      <c r="I179" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I179">
-        <v>2015</v>
       </c>
       <c r="J179">
         <v>2022</v>
@@ -11580,7 +10727,7 @@
         <v>18952.2</v>
       </c>
       <c r="L179">
-        <v>25430.34353582409</v>
+        <v>16441.8</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
@@ -11593,12 +10740,10 @@
         </is>
       </c>
       <c r="O179">
-        <v>16441.8</v>
-      </c>
-      <c r="Q179" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P179">
+        <v>18456.71986595318</v>
       </c>
     </row>
     <row r="180">
@@ -11626,16 +10771,13 @@
           <t>SVN</t>
         </is>
       </c>
-      <c r="G180">
-        <v>1.917694591048416</v>
-      </c>
-      <c r="H180" t="inlineStr">
+      <c r="H180">
+        <v>1.919289150833029</v>
+      </c>
+      <c r="I180" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I180">
-        <v>2015</v>
       </c>
       <c r="J180">
         <v>2022</v>
@@ -11644,7 +10786,7 @@
         <v>25276.8</v>
       </c>
       <c r="L180">
-        <v>30734.82839877017</v>
+        <v>20697</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
@@ -11657,12 +10799,10 @@
         </is>
       </c>
       <c r="O180">
-        <v>20697</v>
-      </c>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P180">
+        <v>23020.64389678337</v>
       </c>
     </row>
     <row r="181">
@@ -11690,16 +10830,13 @@
           <t>SWE</t>
         </is>
       </c>
-      <c r="G181">
-        <v>1.239695496729764</v>
-      </c>
-      <c r="H181" t="inlineStr">
+      <c r="H181">
+        <v>1.223130260369658</v>
+      </c>
+      <c r="I181" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I181">
-        <v>2015</v>
       </c>
       <c r="J181">
         <v>2022</v>
@@ -11708,7 +10845,7 @@
         <v>54878.4</v>
       </c>
       <c r="L181">
-        <v>62849.34372607069</v>
+        <v>51198</v>
       </c>
       <c r="M181" t="inlineStr">
         <is>
@@ -11721,12 +10858,10 @@
         </is>
       </c>
       <c r="O181">
-        <v>51198</v>
-      </c>
-      <c r="Q181" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P181">
+        <v>54210.68852922935</v>
       </c>
     </row>
     <row r="182">
@@ -11754,16 +10889,13 @@
           <t>SWZ</t>
         </is>
       </c>
-      <c r="G182">
-        <v>0.5086410933941546</v>
-      </c>
-      <c r="H182" t="inlineStr">
+      <c r="H182">
+        <v>0.5146098560980599</v>
+      </c>
+      <c r="I182" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I182">
-        <v>2015</v>
       </c>
       <c r="J182">
         <v>2022</v>
@@ -11772,7 +10904,7 @@
         <v>3680.4</v>
       </c>
       <c r="L182">
-        <v>6046.270556982437</v>
+        <v>3420.6</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>
@@ -11785,12 +10917,10 @@
         </is>
       </c>
       <c r="O182">
-        <v>3420.6</v>
-      </c>
-      <c r="Q182" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P182">
+        <v>3942.91247853306</v>
       </c>
     </row>
     <row r="183">
@@ -11818,16 +10948,13 @@
           <t>SXM</t>
         </is>
       </c>
-      <c r="G183">
-        <v>-1.945501706800664</v>
-      </c>
-      <c r="H183" t="inlineStr">
+      <c r="H183">
+        <v>-1.924790634182508</v>
+      </c>
+      <c r="I183" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I183">
-        <v>2015</v>
       </c>
       <c r="J183">
         <v>2022</v>
@@ -11836,7 +10963,7 @@
         <v>32316.6</v>
       </c>
       <c r="L183">
-        <v>49690.43170865651</v>
+        <v>37839.6</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
@@ -11849,12 +10976,10 @@
         </is>
       </c>
       <c r="O183">
-        <v>37839.6</v>
-      </c>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P183">
+        <v>40802.124961508</v>
       </c>
     </row>
     <row r="184">
@@ -11882,16 +11007,13 @@
           <t>SYC</t>
         </is>
       </c>
-      <c r="G184">
-        <v>0.2859994727477247</v>
-      </c>
-      <c r="H184" t="inlineStr">
+      <c r="H184">
+        <v>0.2879461506550943</v>
+      </c>
+      <c r="I184" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I184">
-        <v>2015</v>
       </c>
       <c r="J184">
         <v>2022</v>
@@ -11900,7 +11022,7 @@
         <v>15869.4</v>
       </c>
       <c r="L184">
-        <v>23981.62831596387</v>
+        <v>15333</v>
       </c>
       <c r="M184" t="inlineStr">
         <is>
@@ -11913,12 +11035,10 @@
         </is>
       </c>
       <c r="O184">
-        <v>15333</v>
-      </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P184">
+        <v>17253.46265277846</v>
       </c>
     </row>
     <row r="185">
@@ -11946,16 +11066,13 @@
           <t>SYR</t>
         </is>
       </c>
-      <c r="G185">
-        <v>-1.286169621291654</v>
-      </c>
-      <c r="H185" t="inlineStr">
+      <c r="H185">
+        <v>-1.287186451104751</v>
+      </c>
+      <c r="I185" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I185">
-        <v>2015</v>
       </c>
       <c r="J185">
         <v>2022</v>
@@ -11964,7 +11081,7 @@
         <v>712.1999999999999</v>
       </c>
       <c r="L185">
-        <v>1485.894495602795</v>
+        <v>847.8</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
@@ -11977,12 +11094,10 @@
         </is>
       </c>
       <c r="O185">
-        <v>847.8</v>
-      </c>
-      <c r="Q185" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P185">
+        <v>972.7533282725065</v>
       </c>
     </row>
     <row r="186">
@@ -12010,16 +11125,13 @@
           <t>TCA</t>
         </is>
       </c>
-      <c r="G186">
-        <v>5.91064611583397</v>
-      </c>
-      <c r="H186" t="inlineStr">
+      <c r="H186">
+        <v>5.856702152824515</v>
+      </c>
+      <c r="I186" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I186">
-        <v>2015</v>
       </c>
       <c r="J186">
         <v>2022</v>
@@ -12028,7 +11140,7 @@
         <v>42205.2</v>
       </c>
       <c r="L186">
-        <v>36623.36054529039</v>
+        <v>25736.4</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
@@ -12041,12 +11153,10 @@
         </is>
       </c>
       <c r="O186">
-        <v>25736.4</v>
-      </c>
-      <c r="Q186" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P186">
+        <v>28330.04100469104</v>
       </c>
     </row>
     <row r="187">
@@ -12074,16 +11184,13 @@
           <t>TCD</t>
         </is>
       </c>
-      <c r="G187">
-        <v>-0.4440536654610209</v>
-      </c>
-      <c r="H187" t="inlineStr">
+      <c r="H187">
+        <v>-0.4458190048023515</v>
+      </c>
+      <c r="I187" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I187">
-        <v>2015</v>
       </c>
       <c r="J187">
         <v>2022</v>
@@ -12092,7 +11199,7 @@
         <v>934.8</v>
       </c>
       <c r="L187">
-        <v>1753.091576846247</v>
+        <v>994.1999999999999</v>
       </c>
       <c r="M187" t="inlineStr">
         <is>
@@ -12105,12 +11212,10 @@
         </is>
       </c>
       <c r="O187">
-        <v>994.1999999999999</v>
-      </c>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P187">
+        <v>1142.702531487119</v>
       </c>
     </row>
     <row r="188">
@@ -12138,16 +11243,13 @@
           <t>TGO</t>
         </is>
       </c>
-      <c r="G188">
-        <v>1.017667937714533</v>
-      </c>
-      <c r="H188" t="inlineStr">
+      <c r="H188">
+        <v>1.019076713743634</v>
+      </c>
+      <c r="I188" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I188">
-        <v>2015</v>
       </c>
       <c r="J188">
         <v>2022</v>
@@ -12156,7 +11258,7 @@
         <v>862.8</v>
       </c>
       <c r="L188">
-        <v>1309.065126390442</v>
+        <v>751.1999999999999</v>
       </c>
       <c r="M188" t="inlineStr">
         <is>
@@ -12169,12 +11271,10 @@
         </is>
       </c>
       <c r="O188">
-        <v>751.1999999999999</v>
-      </c>
-      <c r="Q188" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P188">
+        <v>860.5507033979491</v>
       </c>
     </row>
     <row r="189">
@@ -12202,16 +11302,13 @@
           <t>THA</t>
         </is>
       </c>
-      <c r="G189">
-        <v>0.7044875299640491</v>
-      </c>
-      <c r="H189" t="inlineStr">
+      <c r="H189">
+        <v>0.7127585868207648</v>
+      </c>
+      <c r="I189" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I189">
-        <v>2015</v>
       </c>
       <c r="J189">
         <v>2022</v>
@@ -12220,7 +11317,7 @@
         <v>6279</v>
       </c>
       <c r="L189">
-        <v>9841.403518972678</v>
+        <v>5688.599999999999</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
@@ -12233,12 +11330,10 @@
         </is>
       </c>
       <c r="O189">
-        <v>5688.599999999999</v>
-      </c>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P189">
+        <v>6532.480451004234</v>
       </c>
     </row>
     <row r="190">
@@ -12266,16 +11361,13 @@
           <t>TJK</t>
         </is>
       </c>
-      <c r="G190">
-        <v>2.32164732380316</v>
-      </c>
-      <c r="H190" t="inlineStr">
+      <c r="H190">
+        <v>2.33492387201628</v>
+      </c>
+      <c r="I190" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I190">
-        <v>2015</v>
       </c>
       <c r="J190">
         <v>2022</v>
@@ -12284,7 +11376,7 @@
         <v>1326</v>
       </c>
       <c r="L190">
-        <v>1685.287436456043</v>
+        <v>957</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -12297,12 +11389,10 @@
         </is>
       </c>
       <c r="O190">
-        <v>957</v>
-      </c>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P190">
+        <v>1099.529378416387</v>
       </c>
     </row>
     <row r="191">
@@ -12330,16 +11420,13 @@
           <t>TKM</t>
         </is>
       </c>
-      <c r="G191">
-        <v>1.949008098437438</v>
-      </c>
-      <c r="H191" t="inlineStr">
+      <c r="H191">
+        <v>1.971536224624828</v>
+      </c>
+      <c r="I191" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I191">
-        <v>2015</v>
       </c>
       <c r="J191">
         <v>2022</v>
@@ -12348,7 +11435,7 @@
         <v>7551</v>
       </c>
       <c r="L191">
-        <v>9956.675292402862</v>
+        <v>5759.4</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
@@ -12361,12 +11448,10 @@
         </is>
       </c>
       <c r="O191">
-        <v>5759.4</v>
-      </c>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P191">
+        <v>6612.890528315886</v>
       </c>
     </row>
     <row r="192">
@@ -12394,16 +11479,13 @@
           <t>TLS</t>
         </is>
       </c>
-      <c r="G192">
-        <v>1.257425648539286</v>
-      </c>
-      <c r="H192" t="inlineStr">
+      <c r="H192">
+        <v>1.267475311456654</v>
+      </c>
+      <c r="I192" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I192">
-        <v>2015</v>
       </c>
       <c r="J192">
         <v>2022</v>
@@ -12412,7 +11494,7 @@
         <v>1578.6</v>
       </c>
       <c r="L192">
-        <v>2343.208198370996</v>
+        <v>1319.4</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
@@ -12425,12 +11507,10 @@
         </is>
       </c>
       <c r="O192">
-        <v>1319.4</v>
-      </c>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P192">
+        <v>1519.807349455357</v>
       </c>
     </row>
     <row r="193">
@@ -12458,16 +11538,13 @@
           <t>TON</t>
         </is>
       </c>
-      <c r="G193">
-        <v>0.7569220215650725</v>
-      </c>
-      <c r="H193" t="inlineStr">
+      <c r="H193">
+        <v>0.7659334222280572</v>
+      </c>
+      <c r="I193" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I193">
-        <v>2015</v>
       </c>
       <c r="J193">
         <v>2022</v>
@@ -12476,7 +11553,7 @@
         <v>4594.8</v>
       </c>
       <c r="L193">
-        <v>7244.640669091992</v>
+        <v>4123.8</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
@@ -12489,12 +11566,10 @@
         </is>
       </c>
       <c r="O193">
-        <v>4123.8</v>
-      </c>
-      <c r="Q193" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P193">
+        <v>4748.672248673516</v>
       </c>
     </row>
     <row r="194">
@@ -12522,16 +11597,13 @@
           <t>TTO</t>
         </is>
       </c>
-      <c r="G194">
-        <v>-2.033958699186388</v>
-      </c>
-      <c r="H194" t="inlineStr">
+      <c r="H194">
+        <v>-2.044578720359019</v>
+      </c>
+      <c r="I194" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I194">
-        <v>2015</v>
       </c>
       <c r="J194">
         <v>2022</v>
@@ -12540,7 +11612,7 @@
         <v>15721.8</v>
       </c>
       <c r="L194">
-        <v>29752.63435379533</v>
+        <v>19887</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
@@ -12553,12 +11625,10 @@
         </is>
       </c>
       <c r="O194">
-        <v>19887</v>
-      </c>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P194">
+        <v>22158.20356127745</v>
       </c>
     </row>
     <row r="195">
@@ -12586,16 +11656,13 @@
           <t>TUN</t>
         </is>
       </c>
-      <c r="G195">
-        <v>-0.05545647530995065</v>
-      </c>
-      <c r="H195" t="inlineStr">
+      <c r="H195">
+        <v>-0.05611433884518695</v>
+      </c>
+      <c r="I195" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I195">
-        <v>2015</v>
       </c>
       <c r="J195">
         <v>2022</v>
@@ -12604,7 +11671,7 @@
         <v>3983.4</v>
       </c>
       <c r="L195">
-        <v>7060.865503205389</v>
+        <v>4015.2</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
@@ -12617,12 +11684,10 @@
         </is>
       </c>
       <c r="O195">
-        <v>4015.2</v>
-      </c>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P195">
+        <v>4624.401697392432</v>
       </c>
     </row>
     <row r="196">
@@ -12650,16 +11715,13 @@
           <t>TUR</t>
         </is>
       </c>
-      <c r="G196">
-        <v>1.89558879827728</v>
-      </c>
-      <c r="H196" t="inlineStr">
+      <c r="H196">
+        <v>1.912240566487867</v>
+      </c>
+      <c r="I196" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I196">
-        <v>2015</v>
       </c>
       <c r="J196">
         <v>2022</v>
@@ -12668,7 +11730,7 @@
         <v>14055</v>
       </c>
       <c r="L196">
-        <v>18068.02217817668</v>
+        <v>11050.2</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
@@ -12681,12 +11743,10 @@
         </is>
       </c>
       <c r="O196">
-        <v>11050.2</v>
-      </c>
-      <c r="Q196" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P196">
+        <v>12549.72245215359</v>
       </c>
     </row>
     <row r="197">
@@ -12714,16 +11774,13 @@
           <t>TUV</t>
         </is>
       </c>
-      <c r="G197">
-        <v>2.064361066210365</v>
-      </c>
-      <c r="H197" t="inlineStr">
+      <c r="H197">
+        <v>2.088766091122344</v>
+      </c>
+      <c r="I197" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I197">
-        <v>2015</v>
       </c>
       <c r="J197">
         <v>2022</v>
@@ -12732,7 +11789,7 @@
         <v>4515</v>
       </c>
       <c r="L197">
-        <v>5937.930544720187</v>
+        <v>3357.6</v>
       </c>
       <c r="M197" t="inlineStr">
         <is>
@@ -12745,12 +11802,10 @@
         </is>
       </c>
       <c r="O197">
-        <v>3357.6</v>
-      </c>
-      <c r="Q197" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P197">
+        <v>3870.598136034065</v>
       </c>
     </row>
     <row r="198">
@@ -12778,16 +11833,13 @@
           <t>TZA</t>
         </is>
       </c>
-      <c r="G198">
-        <v>0.9407811207719264</v>
-      </c>
-      <c r="H198" t="inlineStr">
+      <c r="H198">
+        <v>0.9449734782067887</v>
+      </c>
+      <c r="I198" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I198">
-        <v>2015</v>
       </c>
       <c r="J198">
         <v>2022</v>
@@ -12796,7 +11848,7 @@
         <v>1070.4</v>
       </c>
       <c r="L198">
-        <v>1652.457724962131</v>
+        <v>939</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
@@ -12809,12 +11861,10 @@
         </is>
       </c>
       <c r="O198">
-        <v>939</v>
-      </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P198">
+        <v>1078.636497029079</v>
       </c>
     </row>
     <row r="199">
@@ -12842,16 +11892,13 @@
           <t>UGA</t>
         </is>
       </c>
-      <c r="G199">
-        <v>0.5678061777964274</v>
-      </c>
-      <c r="H199" t="inlineStr">
+      <c r="H199">
+        <v>0.5695132864764137</v>
+      </c>
+      <c r="I199" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I199">
-        <v>2015</v>
       </c>
       <c r="J199">
         <v>2022</v>
@@ -12860,7 +11907,7 @@
         <v>933</v>
       </c>
       <c r="L199">
-        <v>1513.315692630511</v>
+        <v>862.8</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
@@ -12873,12 +11920,10 @@
         </is>
       </c>
       <c r="O199">
-        <v>862.8</v>
-      </c>
-      <c r="Q199" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P199">
+        <v>990.1717813878786</v>
       </c>
     </row>
     <row r="200">
@@ -12906,16 +11951,13 @@
           <t>UKR</t>
         </is>
       </c>
-      <c r="G200">
-        <v>-0.7703729367345156</v>
-      </c>
-      <c r="H200" t="inlineStr">
+      <c r="H200">
+        <v>-0.7780496869146946</v>
+      </c>
+      <c r="I200" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I200">
-        <v>2015</v>
       </c>
       <c r="J200">
         <v>2022</v>
@@ -12924,7 +11966,7 @@
         <v>1874.4</v>
       </c>
       <c r="L200">
-        <v>3731.237255204751</v>
+        <v>2094.6</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
@@ -12937,12 +11979,10 @@
         </is>
       </c>
       <c r="O200">
-        <v>2094.6</v>
-      </c>
-      <c r="Q200" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P200">
+        <v>2416.476181051201</v>
       </c>
     </row>
     <row r="201">
@@ -12970,16 +12010,13 @@
           <t>URY</t>
         </is>
       </c>
-      <c r="G201">
-        <v>0.5392900772496075</v>
-      </c>
-      <c r="H201" t="inlineStr">
+      <c r="H201">
+        <v>0.5421494821750993</v>
+      </c>
+      <c r="I201" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I201">
-        <v>2015</v>
       </c>
       <c r="J201">
         <v>2022</v>
@@ -12988,7 +12025,7 @@
         <v>18228.6</v>
       </c>
       <c r="L201">
-        <v>26309.06994410842</v>
+        <v>17125.8</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
@@ -13001,12 +12038,10 @@
         </is>
       </c>
       <c r="O201">
-        <v>17125.8</v>
-      </c>
-      <c r="Q201" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P201">
+        <v>19196.050578574</v>
       </c>
     </row>
     <row r="202">
@@ -13034,16 +12069,13 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="G202">
-        <v>2.573309655534128</v>
-      </c>
-      <c r="H202" t="inlineStr">
+      <c r="H202">
+        <v>2.558328340082856</v>
+      </c>
+      <c r="I202" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I202">
-        <v>2015</v>
       </c>
       <c r="J202">
         <v>2022</v>
@@ -13052,7 +12084,7 @@
         <v>64198.2</v>
       </c>
       <c r="L202">
-        <v>68070.4527613938</v>
+        <v>56849.4</v>
       </c>
       <c r="M202" t="inlineStr">
         <is>
@@ -13065,12 +12097,10 @@
         </is>
       </c>
       <c r="O202">
-        <v>56849.4</v>
-      </c>
-      <c r="Q202" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P202">
+        <v>59777.18141740923</v>
       </c>
     </row>
     <row r="203">
@@ -13098,16 +12128,13 @@
           <t>UZB</t>
         </is>
       </c>
-      <c r="G203">
-        <v>1.689024369619444</v>
-      </c>
-      <c r="H203" t="inlineStr">
+      <c r="H203">
+        <v>1.708501522341355</v>
+      </c>
+      <c r="I203" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I203">
-        <v>2015</v>
       </c>
       <c r="J203">
         <v>2022</v>
@@ -13116,7 +12143,7 @@
         <v>3576.6</v>
       </c>
       <c r="L203">
-        <v>4977.499374929</v>
+        <v>2803.2</v>
       </c>
       <c r="M203" t="inlineStr">
         <is>
@@ -13129,12 +12156,10 @@
         </is>
       </c>
       <c r="O203">
-        <v>2803.2</v>
-      </c>
-      <c r="Q203" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P203">
+        <v>3233.336167128301</v>
       </c>
     </row>
     <row r="204">
@@ -13162,16 +12187,13 @@
           <t>VCT</t>
         </is>
       </c>
-      <c r="G204">
-        <v>1.082794041319179</v>
-      </c>
-      <c r="H204" t="inlineStr">
+      <c r="H204">
+        <v>1.094821298237775</v>
+      </c>
+      <c r="I204" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I204">
-        <v>2015</v>
       </c>
       <c r="J204">
         <v>2022</v>
@@ -13180,7 +12202,7 @@
         <v>8524.199999999999</v>
       </c>
       <c r="L204">
-        <v>12503.22561122597</v>
+        <v>7353.599999999999</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
@@ -13193,12 +12215,10 @@
         </is>
       </c>
       <c r="O204">
-        <v>7353.599999999999</v>
-      </c>
-      <c r="Q204" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P204">
+        <v>8416.676083883847</v>
       </c>
     </row>
     <row r="205">
@@ -13226,16 +12246,13 @@
           <t>VIR</t>
         </is>
       </c>
-      <c r="G205">
-        <v>1.044047383040899</v>
-      </c>
-      <c r="H205" t="inlineStr">
+      <c r="H205">
+        <v>1.032508579281674</v>
+      </c>
+      <c r="I205" t="inlineStr">
         <is>
           <t>40-60</t>
         </is>
-      </c>
-      <c r="I205">
-        <v>2015</v>
       </c>
       <c r="J205">
         <v>2022</v>
@@ -13244,7 +12261,7 @@
         <v>36983.4</v>
       </c>
       <c r="L205">
-        <v>45685.1970926893</v>
+        <v>34007.4</v>
       </c>
       <c r="M205" t="inlineStr">
         <is>
@@ -13257,12 +12274,10 @@
         </is>
       </c>
       <c r="O205">
-        <v>34007.4</v>
-      </c>
-      <c r="Q205" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P205">
+        <v>36888.57519088667</v>
       </c>
     </row>
     <row r="206">
@@ -13290,16 +12305,13 @@
           <t>VNM</t>
         </is>
       </c>
-      <c r="G206">
-        <v>2.348375162142592</v>
-      </c>
-      <c r="H206" t="inlineStr">
+      <c r="H206">
+        <v>2.375249387040327</v>
+      </c>
+      <c r="I206" t="inlineStr">
         <is>
           <t>80-100</t>
         </is>
-      </c>
-      <c r="I206">
-        <v>2015</v>
       </c>
       <c r="J206">
         <v>2022</v>
@@ -13308,7 +12320,7 @@
         <v>3617.4</v>
       </c>
       <c r="L206">
-        <v>4583.019547475574</v>
+        <v>2577.6</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
@@ -13321,12 +12333,10 @@
         </is>
       </c>
       <c r="O206">
-        <v>2577.6</v>
-      </c>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P206">
+        <v>2973.555447345798</v>
       </c>
     </row>
     <row r="207">
@@ -13354,16 +12364,13 @@
           <t>VUT</t>
         </is>
       </c>
-      <c r="G207">
-        <v>-0.2835303528315843</v>
-      </c>
-      <c r="H207" t="inlineStr">
+      <c r="H207">
+        <v>-0.2867222702377603</v>
+      </c>
+      <c r="I207" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I207">
-        <v>2015</v>
       </c>
       <c r="J207">
         <v>2022</v>
@@ -13372,7 +12379,7 @@
         <v>2740.2</v>
       </c>
       <c r="L207">
-        <v>5067.42742227595</v>
+        <v>2854.8</v>
       </c>
       <c r="M207" t="inlineStr">
         <is>
@@ -13385,12 +12392,10 @@
         </is>
       </c>
       <c r="O207">
-        <v>2854.8</v>
-      </c>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P207">
+        <v>3292.716413282088</v>
       </c>
     </row>
     <row r="208">
@@ -13418,16 +12423,13 @@
           <t>WSM</t>
         </is>
       </c>
-      <c r="G208">
-        <v>-0.6688231790753077</v>
-      </c>
-      <c r="H208" t="inlineStr">
+      <c r="H208">
+        <v>-0.6767413038931807</v>
+      </c>
+      <c r="I208" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I208">
-        <v>2015</v>
       </c>
       <c r="J208">
         <v>2022</v>
@@ -13436,7 +12438,7 @@
         <v>3710.4</v>
       </c>
       <c r="L208">
-        <v>7177.683132194268</v>
+        <v>4084.2</v>
       </c>
       <c r="M208" t="inlineStr">
         <is>
@@ -13449,12 +12451,10 @@
         </is>
       </c>
       <c r="O208">
-        <v>4084.2</v>
-      </c>
-      <c r="Q208" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P208">
+        <v>4703.365136496057</v>
       </c>
     </row>
     <row r="209">
@@ -13482,16 +12482,13 @@
           <t>XKX</t>
         </is>
       </c>
-      <c r="G209">
-        <v>1.96596187180646</v>
-      </c>
-      <c r="H209" t="inlineStr">
+      <c r="H209">
+        <v>1.989269301032948</v>
+      </c>
+      <c r="I209" t="inlineStr">
         <is>
           <t>60-80</t>
         </is>
-      </c>
-      <c r="I209">
-        <v>2015</v>
       </c>
       <c r="J209">
         <v>2022</v>
@@ -13500,7 +12497,7 @@
         <v>4666.2</v>
       </c>
       <c r="L209">
-        <v>6218.24893337892</v>
+        <v>3520.8</v>
       </c>
       <c r="M209" t="inlineStr">
         <is>
@@ -13513,12 +12510,10 @@
         </is>
       </c>
       <c r="O209">
-        <v>3520.8</v>
-      </c>
-      <c r="Q209" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P209">
+        <v>4057.883999603362</v>
       </c>
     </row>
     <row r="210">
@@ -13546,25 +12541,11 @@
           <t>YEM</t>
         </is>
       </c>
-      <c r="G210">
-        <v>-2.92538623650589</v>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>0-20</t>
-        </is>
-      </c>
-      <c r="I210">
-        <v>2015</v>
-      </c>
       <c r="J210">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="K210">
-        <v>903.6</v>
-      </c>
-      <c r="L210">
-        <v>2420.166235902503</v>
+        <v>1079.3293837659</v>
       </c>
       <c r="M210" t="inlineStr">
         <is>
@@ -13574,14 +12555,6 @@
       <c r="N210" t="inlineStr">
         <is>
           <t>GDP per capita (constant 2015 US$)</t>
-        </is>
-      </c>
-      <c r="O210">
-        <v>1362</v>
-      </c>
-      <c r="Q210" t="inlineStr">
-        <is>
-          <t>never</t>
         </is>
       </c>
     </row>
@@ -13610,16 +12583,13 @@
           <t>ZAF</t>
         </is>
       </c>
-      <c r="G211">
-        <v>-0.3935807341051105</v>
-      </c>
-      <c r="H211" t="inlineStr">
+      <c r="H211">
+        <v>-0.3982049172545276</v>
+      </c>
+      <c r="I211" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
-      </c>
-      <c r="I211">
-        <v>2015</v>
       </c>
       <c r="J211">
         <v>2022</v>
@@ -13628,7 +12598,7 @@
         <v>5784</v>
       </c>
       <c r="L211">
-        <v>10528.28098803841</v>
+        <v>6112.2</v>
       </c>
       <c r="M211" t="inlineStr">
         <is>
@@ -13641,12 +12611,10 @@
         </is>
       </c>
       <c r="O211">
-        <v>6112.2</v>
-      </c>
-      <c r="Q211" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P211">
+        <v>7013.194038742172</v>
       </c>
     </row>
     <row r="212">
@@ -13674,16 +12642,13 @@
           <t>ZMB</t>
         </is>
       </c>
-      <c r="G212">
-        <v>0.01629921814054975</v>
-      </c>
-      <c r="H212" t="inlineStr">
+      <c r="H212">
+        <v>0.01641533685955616</v>
+      </c>
+      <c r="I212" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I212">
-        <v>2015</v>
       </c>
       <c r="J212">
         <v>2022</v>
@@ -13692,7 +12657,7 @@
         <v>1299</v>
       </c>
       <c r="L212">
-        <v>2300.901811316148</v>
+        <v>1296</v>
       </c>
       <c r="M212" t="inlineStr">
         <is>
@@ -13705,12 +12670,10 @@
         </is>
       </c>
       <c r="O212">
-        <v>1296</v>
-      </c>
-      <c r="Q212" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P212">
+        <v>1492.691115939467</v>
       </c>
     </row>
     <row r="213">
@@ -13738,16 +12701,13 @@
           <t>ZWE</t>
         </is>
       </c>
-      <c r="G213">
-        <v>-0.0918032150234548</v>
-      </c>
-      <c r="H213" t="inlineStr">
+      <c r="H213">
+        <v>-0.0925055216787192</v>
+      </c>
+      <c r="I213" t="inlineStr">
         <is>
           <t>20-40</t>
         </is>
-      </c>
-      <c r="I213">
-        <v>2015</v>
       </c>
       <c r="J213">
         <v>2022</v>
@@ -13756,7 +12716,7 @@
         <v>1368.6</v>
       </c>
       <c r="L213">
-        <v>2464.569415792426</v>
+        <v>1386.6</v>
       </c>
       <c r="M213" t="inlineStr">
         <is>
@@ -13769,12 +12729,10 @@
         </is>
       </c>
       <c r="O213">
-        <v>1386.6</v>
-      </c>
-      <c r="Q213" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
+        <v>2015</v>
+      </c>
+      <c r="P213">
+        <v>1597.663127620486</v>
       </c>
     </row>
   </sheetData>
